--- a/tame_output/ON/bt/strategyON_20240920.xlsx
+++ b/tame_output/ON/bt/strategyON_20240920.xlsx
@@ -49667,10 +49667,10 @@
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.21647906978756</v>
+        <v>-4.216297530810931</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.237312413759563</v>
+        <v>3.237385029350215</v>
       </c>
       <c r="F2092" t="n">
         <v>1.439193895580174</v>

--- a/tame_output/ON/bt/strategyON_20240920.xlsx
+++ b/tame_output/ON/bt/strategyON_20240920.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>115.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>180.8%</t>
+          <t>183.1%</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.2%</t>
+          <t>-583.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-52.5%</t>
+          <t>-50.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.8%</t>
+          <t>132.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>120.7%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>132.8%</t>
+          <t>135.1%</t>
         </is>
       </c>
     </row>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.704757949437327</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236293</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.01229636333295</v>
+        <v>4.035516938641222</v>
       </c>
       <c r="D2072" t="n">
         <v>-4.383105588654425</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.258697703557432</v>
+        <v>2.281918278865704</v>
       </c>
       <c r="F2072" t="n">
         <v>1.231445585734082</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.751163714773399</v>
+        <v>4.774384290081671</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.013547445525788</v>
+        <v>4.03676802083406</v>
       </c>
       <c r="D2073" t="n">
         <v>-4.468961617994392</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.225606374014283</v>
+        <v>2.248826949322555</v>
       </c>
       <c r="F2073" t="n">
         <v>1.189069516507947</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.726989155430556</v>
+        <v>4.750209730738828</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610378</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>4.019187222654562</v>
       </c>
       <c r="D2074" t="n">
         <v>-4.477798415410511</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.204490856868337</v>
+        <v>2.227711432176609</v>
       </c>
       <c r="F2074" t="n">
         <v>1.181627343866596</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.704943053666248</v>
+        <v>4.72816362897452</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.71554441166745</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>4.029351733699611</v>
       </c>
       <c r="D2075" t="n">
         <v>-4.56918097797597</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.178102342887203</v>
+        <v>2.201322918195475</v>
       </c>
       <c r="F2075" t="n">
         <v>1.145062459147252</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.69316863387969</v>
+        <v>4.716389209187962</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.131479991523879</v>
       </c>
       <c r="D2076" t="n">
         <v>-4.557474259988964</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.284913287906273</v>
+        <v>2.308133863214545</v>
       </c>
       <c r="F2076" t="n">
         <v>1.156769177134258</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.802320922496161</v>
+        <v>4.825541497804434</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.134512330255284</v>
       </c>
       <c r="D2077" t="n">
         <v>-4.457810755905301</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.327811028271142</v>
+        <v>2.351031603579415</v>
       </c>
       <c r="F2077" t="n">
         <v>1.219956260337945</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.843265511149778</v>
+        <v>4.866486086458051</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452568</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.347417163533342</v>
       </c>
       <c r="D2078" t="n">
         <v>-4.468126854071653</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.53658942228266</v>
+        <v>2.559809997590932</v>
       </c>
       <c r="F2078" t="n">
         <v>1.219956260337945</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.056170344427836</v>
+        <v>5.079390919736109</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.346595830445431</v>
       </c>
       <c r="D2079" t="n">
         <v>-4.468032886054281</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.535805676401699</v>
+        <v>2.559026251709971</v>
       </c>
       <c r="F2079" t="n">
         <v>1.220326121685263</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.055570928148317</v>
+        <v>5.078791503456589</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.340827816389785</v>
       </c>
       <c r="D2080" t="n">
         <v>-4.475251710254125</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.527150132666115</v>
+        <v>2.550370707974387</v>
       </c>
       <c r="F2080" t="n">
         <v>1.220326121685263</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.049802914092671</v>
+        <v>5.073023489400943</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.340827816389785</v>
       </c>
       <c r="D2081" t="n">
         <v>-4.474303287136086</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.52752950191333</v>
+        <v>2.550750077221602</v>
       </c>
       <c r="F2081" t="n">
         <v>1.220326121685263</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.049802914092671</v>
+        <v>5.073023489400943</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.353555424370877</v>
       </c>
       <c r="D2082" t="n">
         <v>-4.631371745391711</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.477429726592173</v>
+        <v>2.500650301900445</v>
       </c>
       <c r="F2082" t="n">
         <v>1.220326121685263</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.062530522073763</v>
+        <v>5.085751097382035</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.355501422795265</v>
       </c>
       <c r="D2083" t="n">
         <v>-4.625379498602899</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.481772623732085</v>
+        <v>2.504993199040357</v>
       </c>
       <c r="F2083" t="n">
         <v>1.220326121685263</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.06447652049815</v>
+        <v>5.087697095806423</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.349155558813034</v>
       </c>
       <c r="D2084" t="n">
         <v>-4.536821537472131</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.510849944202161</v>
+        <v>2.534070519510433</v>
       </c>
       <c r="F2084" t="n">
         <v>1.220326121685263</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.058130656515919</v>
+        <v>5.081351231824192</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.348464236252029</v>
       </c>
       <c r="D2085" t="n">
         <v>-4.519062459969057</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.517262252642386</v>
+        <v>2.540482827950658</v>
       </c>
       <c r="F2085" t="n">
         <v>1.220326121685263</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.057439333954915</v>
+        <v>5.080659909263187</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.361246422160616</v>
       </c>
       <c r="D2086" t="n">
         <v>-4.41943230891999</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.5698964989706</v>
+        <v>2.593117074278872</v>
       </c>
       <c r="F2086" t="n">
         <v>1.31995627273433</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.129999610492942</v>
+        <v>5.153220185801215</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.550400687659343</v>
       </c>
       <c r="D2087" t="n">
         <v>-4.468831817609001</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.739290960993722</v>
+        <v>2.762511536301994</v>
       </c>
       <c r="F2087" t="n">
         <v>1.330215106166075</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.325309176050715</v>
+        <v>5.348529751358988</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.537589360762205</v>
       </c>
       <c r="D2088" t="n">
         <v>-4.262147343966625</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.809153423553535</v>
+        <v>2.832373998861807</v>
       </c>
       <c r="F2088" t="n">
         <v>1.536899579808451</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.436508533339003</v>
+        <v>5.459729108647275</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.516370299108037</v>
+        <v>4.53959087441631</v>
       </c>
       <c r="D2089" t="n">
         <v>-4.296304238964151</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.797492179208629</v>
+        <v>2.820712754516901</v>
       </c>
       <c r="F2089" t="n">
         <v>1.453315810267638</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.38835978526862</v>
+        <v>5.411580360576893</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.782482115652378</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.869867413097705</v>
+        <v>4.893087988405977</v>
       </c>
       <c r="D2090" t="n">
         <v>-4.203714759902694</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.188025084822879</v>
+        <v>3.211245660131151</v>
       </c>
       <c r="F2090" t="n">
         <v>1.453315810267638</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.741856899258288</v>
+        <v>5.76507747456656</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108667</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.874430524664808</v>
+        <v>4.89765109997308</v>
       </c>
       <c r="D2091" t="n">
         <v>-4.263603387726245</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.168632745260562</v>
+        <v>3.191853320568835</v>
       </c>
       <c r="F2091" t="n">
         <v>1.439193895580174</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.737946862012913</v>
+        <v>5.761167437321185</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.764640745439924</v>
+        <v>3.759762930675179</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.924260465988335</v>
+        <v>4.947481041296608</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.216297530810931</v>
+        <v>-4.215637739998877</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.237385029350215</v>
+        <v>3.260869520983309</v>
       </c>
       <c r="F2092" t="n">
         <v>1.439193895580174</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.78777680333644</v>
+        <v>5.810997378644712</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240920.xlsx
+++ b/tame_output/ON/bt/strategyON_20240920.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>115.7%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>183.1%</t>
+          <t>180.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.1%</t>
+          <t>-591.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-50.1%</t>
+          <t>-55.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>113.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.3%</t>
+          <t>-321.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-78.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.7%</t>
+          <t>132.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>120.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>135.1%</t>
+          <t>134.0%</t>
         </is>
       </c>
     </row>
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.95866307850059</v>
+        <v>-2.929162138771642</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.016675450501039</v>
+        <v>2.028475826392619</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9820880170877296</v>
+        <v>0.9937676410940548</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.789749916467661</v>
+        <v>3.796757690871456</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.06696374037071</v>
+        <v>-3.037462800641762</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.98642859261891</v>
+        <v>1.998228968510489</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9820880170877296</v>
+        <v>0.9937676410940548</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.80282332333358</v>
+        <v>3.809831097737375</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.084767712091454</v>
+        <v>-3.055266772362506</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.971312200713553</v>
+        <v>1.983112576605132</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9115533941825285</v>
+        <v>0.9232330181888537</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.752507746373399</v>
+        <v>3.759515520777194</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.112668499200927</v>
+        <v>-3.083167559471979</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.958675926996765</v>
+        <v>1.970476302888344</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8769564700395936</v>
+        <v>0.8886360940459189</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.73027363301464</v>
+        <v>3.737281407418435</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.23519460190382</v>
+        <v>-3.205693662174873</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.906429929892806</v>
+        <v>1.918230305784386</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7544303673366998</v>
+        <v>0.766109991343025</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.653522415370103</v>
+        <v>3.660530189773898</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.465709098089409</v>
+        <v>-3.436208158360461</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.880930091009075</v>
+        <v>1.892730466900654</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.523915871151111</v>
+        <v>0.5355954951574363</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.581919677249253</v>
+        <v>3.588927451653048</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.814454183313853</v>
+        <v>-3.784953243584905</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.881743775921144</v>
+        <v>1.893544151812724</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.4268475412385385</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.656982623899762</v>
+        <v>3.663990398303557</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.968440601089993</v>
+        <v>-3.938939661361045</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.889129477956328</v>
+        <v>1.900929853847907</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.4268475412385385</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.725962893045402</v>
+        <v>3.732970667449197</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.173040035953002</v>
+        <v>-4.143539096224054</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.793340906131246</v>
+        <v>1.805141282022825</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.4268475412385385</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.712014095165522</v>
+        <v>3.719021869569318</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.425515189960726</v>
+        <v>-4.396014250231778</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.70422133358357</v>
+        <v>1.716021709475149</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.4268475412385385</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.723884584220936</v>
+        <v>3.730892358624732</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.718410946440138</v>
+        <v>-4.688910006711191</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.588273565510748</v>
+        <v>1.600073941402328</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.4268475412385385</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.72509511873988</v>
+        <v>3.732102893143675</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.905075074574946</v>
+        <v>-4.875574134845999</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.517729656484147</v>
+        <v>1.529530032375726</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3884289464076534</v>
+        <v>0.4001085704139786</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.713173478472465</v>
+        <v>3.720181252876261</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.051095761488908</v>
+        <v>-5.021594821759961</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.454399234454751</v>
+        <v>1.46619961034633</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.3910254786201217</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.702801476132341</v>
+        <v>3.709809250536136</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.142809770598493</v>
+        <v>-5.113308830869546</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.579917687509961</v>
+        <v>1.591718063401541</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.3910254786201217</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.865005532831385</v>
+        <v>3.87201330723518</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.174461429658463</v>
+        <v>-5.144960489929515</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.562103661849788</v>
+        <v>1.573904037741367</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3741773973693562</v>
+        <v>0.3858570213756815</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.856751096448535</v>
+        <v>3.86375887085233</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.243527484231399</v>
+        <v>-5.214026544502452</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.544706657589105</v>
+        <v>1.556507033480683</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3118065198757461</v>
+        <v>0.3234861438820714</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.82955798752086</v>
+        <v>3.836565761924655</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.345503606479807</v>
+        <v>-5.316002666750859</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.512841847145644</v>
+        <v>1.524642223037223</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2098303976273386</v>
+        <v>0.2215100216336638</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.777297952627718</v>
+        <v>3.784305727031513</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.235497323002585</v>
+        <v>-5.316212433604777</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.548997247780708</v>
+        <v>1.516711203539831</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2330349695446138</v>
+        <v>0.2267224964254927</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.783373583022259</v>
+        <v>3.779586099150786</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.092437747261659</v>
+        <v>-5.173152857863851</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.610471088799053</v>
+        <v>1.578185044558176</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2410483961345931</v>
+        <v>0.234735923015472</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.79243164969822</v>
+        <v>3.788644165826748</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.790991021789822</v>
+        <v>-4.871706132392013</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.738310661870324</v>
+        <v>1.706024617629447</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.5361826484873092</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.980560567863859</v>
+        <v>3.976773083992386</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.815581266025005</v>
+        <v>-4.896296376627197</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.729445741928961</v>
+        <v>1.697159697688084</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.5361826484873092</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.98153174561657</v>
+        <v>3.977744261745096</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.764542890018485</v>
+        <v>-4.845258000620677</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.750703996711324</v>
+        <v>1.718417952470447</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.5361826484873092</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.982374649996325</v>
+        <v>3.978587166124852</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.723403595151854</v>
+        <v>-4.804118705754046</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.786197813532122</v>
+        <v>1.753911769291245</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5836344164730611</v>
+        <v>0.57732194335394</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.026096325790449</v>
+        <v>4.022308841918976</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.626768683133214</v>
+        <v>-4.707483793735406</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.641035774463513</v>
+        <v>1.608749730222636</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6802693284917011</v>
+        <v>0.67395685537258</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.900261269125567</v>
+        <v>3.896473785254094</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.557730672184746</v>
+        <v>-4.638445782786938</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.672153022916864</v>
+        <v>1.639866978675987</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7493073394401691</v>
+        <v>0.7429948663210481</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.945186119768612</v>
+        <v>3.94139863589714</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.393234337993785</v>
+        <v>-4.473949448595977</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.722378375669331</v>
+        <v>1.690092331428454</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.913803673631131</v>
+        <v>0.9074912005120099</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.028310739359272</v>
+        <v>4.024523255487799</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.316135736451912</v>
+        <v>-4.396850847054104</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.75240552672251</v>
+        <v>1.720119482481633</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.913803673631131</v>
+        <v>0.9074912005120099</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.027498449795702</v>
+        <v>4.023710965924229</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.326520931341801</v>
+        <v>-4.407236041943993</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.758120227891627</v>
+        <v>1.72583418365075</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9034184787412417</v>
+        <v>0.8971060056221206</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.03113611198684</v>
+        <v>4.027348628115368</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.345109090064026</v>
+        <v>-4.425824200666218</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.821521970179162</v>
+        <v>1.789235925938285</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8848303200190164</v>
+        <v>0.8785178468998953</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.09082022252993</v>
+        <v>4.087032738658458</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.345407636760062</v>
+        <v>-4.426122747362254</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.818271562319046</v>
+        <v>1.785985518078169</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8845317733229805</v>
+        <v>0.8782193002038594</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.087510105330607</v>
+        <v>4.083722621459135</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.244584503069635</v>
+        <v>-4.325299613671826</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.863131710734609</v>
+        <v>1.830845666493732</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8969959888073343</v>
+        <v>0.8906835156882132</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.099519529560611</v>
+        <v>4.095732045689139</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.053803142317227</v>
+        <v>-4.134518252919419</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.939573508514115</v>
+        <v>1.907287464273238</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.087777349559742</v>
+        <v>1.081464876440621</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.214117599490599</v>
+        <v>4.210330115619126</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.946839784467805</v>
+        <v>-4.027554895069997</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.96219569739148</v>
+        <v>1.929909653150603</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.146241957519543</v>
+        <v>1.139929484400422</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.229033210004077</v>
+        <v>4.225245726132604</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.891509196566043</v>
+        <v>-3.972224307168235</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.019294869164243</v>
+        <v>1.987008824923366</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.201572545421305</v>
+        <v>1.195260072302184</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.297198499357192</v>
+        <v>4.293411015485719</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.87945506965308</v>
+        <v>-3.960170180255272</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.017803087830866</v>
+        <v>1.985517043589989</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.213626672334268</v>
+        <v>1.207314199215147</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.298117543406407</v>
+        <v>4.294330059534935</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.920610189221301</v>
+        <v>-4.001325299823494</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.003221670187714</v>
+        <v>1.970935625946837</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.172471552766047</v>
+        <v>1.166159079646926</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.275305101849611</v>
+        <v>4.271517617978138</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.852561626529771</v>
+        <v>-3.933276737131964</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.043292121142208</v>
+        <v>2.011006076901332</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>1.234207642338456</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.325197781470939</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.084162019699273</v>
+        <v>-4.164877130301464</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.970854634048002</v>
+        <v>1.938568589807125</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>1.234207642338456</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.345400451644533</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134213565228492</v>
+        <v>-4.214928675830684</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934440251903196</v>
+        <v>1.902154207662319</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>1.234207642338456</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.329006687711415</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309320397804937</v>
+        <v>-4.390035508407129</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824649432466085</v>
+        <v>1.792363388225208</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>1.234207642338456</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.289258601304882</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113220244374414</v>
+        <v>-4.193935354976606</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910112112835234</v>
+        <v>1.877826068594357</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.430307795768979</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.413941312360135</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96019485226113</v>
+        <v>-4.040909962863322</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070493269253452</v>
+        <v>2.038207225012576</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.583333187882263</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.60492754720101</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.9885021661344</v>
+        <v>-4.069217276736592</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246636568612437</v>
+        <v>2.21435052437156</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.583333187882263</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.792393772109302</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155095391247922</v>
+        <v>-4.235810501850114</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14940222992111</v>
+        <v>2.117116185680234</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.41673996276874</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.661840788395271</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132059597886356</v>
+        <v>-4.212774708488548</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.162292949927454</v>
+        <v>2.130006905686578</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.41673996276874</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.665517191056989</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.10281361743066</v>
+        <v>-4.183528728032852</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171609397233228</v>
+        <v>2.139323352992351</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.41673996276874</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.663135246180484</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.209739165308511</v>
+        <v>-4.290454275910703</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.126132417239723</v>
+        <v>2.093846372998846</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>1.309814414890889</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.596273156611409</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.35475772381576</v>
+        <v>-4.435472834417951</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069553795980058</v>
+        <v>2.037267751739181</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>1.16479585638364</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.510690823650294</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473099489600477</v>
+        <v>-4.553814600202669</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.122148328923924</v>
+        <v>2.089862284683047</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>1.175481894946531</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.617033686045781</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524509911921185</v>
+        <v>-4.605225022523377</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099369857121579</v>
+        <v>2.067083812880703</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>1.175481894946531</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.61481938317172</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437327</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603929363128937</v>
+        <v>-4.684644473731129</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067505204712768</v>
+        <v>2.035219160471891</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>1.175481894946531</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.61472251124601</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699392361046154</v>
+        <v>-4.780107471648346</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.029313899103924</v>
+        <v>1.997027854863047</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>1.175481894946531</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.614716404804052</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635016450195439</v>
+        <v>-4.715731560797631</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053160660006821</v>
+        <v>2.020874615765944</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>1.239857805797246</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.651438347877092</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690385612327633</v>
+        <v>-4.771100722929825</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036746812901669</v>
+        <v>2.004460768660793</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>1.239857805797246</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.657172165624819</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.73582339215846</v>
+        <v>-4.816538502760652</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.018110064312271</v>
+        <v>1.985824020071394</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.203325288238207</v>
+        <v>1.197012815119086</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.634791018432328</v>
+        <v>4.631003534560856</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.647616558010882</v>
+        <v>-4.728331668613074</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.073267190821621</v>
+        <v>2.040981146580744</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.203325288238207</v>
+        <v>1.197012815119086</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.654665411282647</v>
+        <v>4.650877927411174</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.541581562805573</v>
+        <v>-4.622296673407765</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.099381889428473</v>
+        <v>2.067095845187596</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.203325288238207</v>
+        <v>1.197012815119086</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.638366111807374</v>
+        <v>4.634578627935902</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.358369899672478</v>
+        <v>-4.43908501027467</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.175097504145756</v>
+        <v>2.14281145990488</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.203325288238207</v>
+        <v>1.197012815119086</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.64079706127142</v>
+        <v>4.637009577399947</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.286648452658627</v>
+        <v>-4.367363563260819</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.169577268799187</v>
+        <v>2.13729122455831</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.275046735252058</v>
+        <v>1.268734262132937</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.64962111532762</v>
+        <v>4.645833631456147</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.26427542705092</v>
+        <v>-4.344990537653112</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.125442224963441</v>
+        <v>2.093156180722564</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.286302486364959</v>
+        <v>1.279990013245838</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.603290311916533</v>
+        <v>4.59950282804506</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.297291722961665</v>
+        <v>-4.378006833563857</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.297433911484498</v>
+        <v>2.265147867243621</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.216865109698208</v>
+        <v>1.210552636579087</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.746826090801837</v>
+        <v>4.743038606930364</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883673</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.285764087312057</v>
+        <v>-4.366479197914249</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.29396619157259</v>
+        <v>2.261680147331714</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.27586576789957</v>
+        <v>1.269553294780449</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.774147711550904</v>
+        <v>4.770360227679431</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236293</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.035516938641222</v>
+        <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.383105588654425</v>
+        <v>-4.415892609334863</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.281918278865704</v>
+        <v>2.245582895285256</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.231445585734082</v>
+        <v>1.252596831038402</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.774384290081671</v>
+        <v>4.763854461955991</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.03676802083406</v>
+        <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.468961617994392</v>
+        <v>-4.50174863867483</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.248826949322555</v>
+        <v>2.212491565742108</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.189069516507947</v>
+        <v>1.210220761812267</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.750209730738828</v>
+        <v>4.739679902613148</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610378</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.019187222654562</v>
+        <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.477798415410511</v>
+        <v>-4.510585436090949</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.227711432176609</v>
+        <v>2.191376048596162</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.181627343866596</v>
+        <v>1.202778589170916</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.72816362897452</v>
+        <v>4.71763380084884</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71554441166745</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.029351733699611</v>
+        <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.56918097797597</v>
+        <v>-4.601967998656407</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.201322918195475</v>
+        <v>2.164987534615028</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.145062459147252</v>
+        <v>1.166213704451572</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.716389209187962</v>
+        <v>4.705859381062282</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.131479991523879</v>
+        <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.557474259988964</v>
+        <v>-4.590261280669401</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.308133863214545</v>
+        <v>2.271798479634098</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.156769177134258</v>
+        <v>1.177920422438578</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.825541497804434</v>
+        <v>4.815011669678753</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.134512330255284</v>
+        <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.457810755905301</v>
+        <v>-4.490597776585739</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.351031603579415</v>
+        <v>2.314696219998968</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.219956260337945</v>
+        <v>1.241107505642265</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.866486086458051</v>
+        <v>4.855956258332371</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452568</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.347417163533342</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.468126854071653</v>
+        <v>-4.500913874752091</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.559809997590932</v>
+        <v>2.523474614010485</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.219956260337945</v>
+        <v>1.241107505642265</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.079390919736109</v>
+        <v>5.068861091610429</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.346595830445431</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.468032886054281</v>
+        <v>-4.500819906734718</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.559026251709971</v>
+        <v>2.522690868129524</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.220326121685263</v>
+        <v>1.241477366989583</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.078791503456589</v>
+        <v>5.068261675330909</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988013</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.340827816389785</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.475251710254125</v>
+        <v>-4.508038730934563</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.550370707974387</v>
+        <v>2.51403532439394</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.220326121685263</v>
+        <v>1.241477366989583</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.073023489400943</v>
+        <v>5.062493661275263</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740918</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.340827816389785</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.474303287136086</v>
+        <v>-4.507090307816524</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.550750077221602</v>
+        <v>2.514414693641155</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.220326121685263</v>
+        <v>1.241477366989583</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.073023489400943</v>
+        <v>5.062493661275263</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.353555424370877</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.631371745391711</v>
+        <v>-4.664158766072148</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.500650301900445</v>
+        <v>2.464314918319998</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.220326121685263</v>
+        <v>1.241477366989583</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.085751097382035</v>
+        <v>5.075221269256355</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.355501422795265</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.625379498602899</v>
+        <v>-4.658166519283337</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.504993199040357</v>
+        <v>2.46865781545991</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.220326121685263</v>
+        <v>1.241477366989583</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.087697095806423</v>
+        <v>5.077167267680743</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.349155558813034</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.536821537472131</v>
+        <v>-4.569608558152569</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.534070519510433</v>
+        <v>2.497735135929986</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.220326121685263</v>
+        <v>1.241477366989583</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.081351231824192</v>
+        <v>5.070821403698512</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383087</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.348464236252029</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.519062459969057</v>
+        <v>-4.551849480649495</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.540482827950658</v>
+        <v>2.504147444370211</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.220326121685263</v>
+        <v>1.241477366989583</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.080659909263187</v>
+        <v>5.070130081137507</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.361246422160616</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.41943230891999</v>
+        <v>-4.452219329600427</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.593117074278872</v>
+        <v>2.556781690698425</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.31995627273433</v>
+        <v>1.34110751803865</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.153220185801215</v>
+        <v>5.142690357675535</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455267</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.550400687659343</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.468831817609001</v>
+        <v>-4.501618838289438</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.762511536301994</v>
+        <v>2.726176152721547</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.330215106166075</v>
+        <v>1.351366351470395</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.348529751358988</v>
+        <v>5.337999923233308</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.537589360762205</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.262147343966625</v>
+        <v>-4.294934364647062</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.832373998861807</v>
+        <v>2.796038615281359</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.536899579808451</v>
+        <v>1.558050825112771</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.459729108647275</v>
+        <v>5.449199280521595</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.53959087441631</v>
+        <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.296304238964151</v>
+        <v>-4.329091259644589</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.820712754516901</v>
+        <v>2.784377370936454</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.453315810267638</v>
+        <v>1.474467055571958</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.411580360576893</v>
+        <v>5.401050532451213</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652378</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.893087988405977</v>
+        <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.203714759902694</v>
+        <v>-4.236501780583132</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.211245660131151</v>
+        <v>3.174910276550704</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.453315810267638</v>
+        <v>1.474467055571958</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.76507747456656</v>
+        <v>5.75454764644088</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108667</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.89765109997308</v>
+        <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.263603387726245</v>
+        <v>-4.296390408406682</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.191853320568835</v>
+        <v>3.155517936988387</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.439193895580174</v>
+        <v>1.460345140884494</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.761167437321185</v>
+        <v>5.750637609195504</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.759762930675179</v>
+        <v>3.860249295492581</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.947481041296608</v>
+        <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.215637739998877</v>
+        <v>-4.300261802518784</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.260869520983309</v>
+        <v>3.203799320667074</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.439193895580174</v>
+        <v>1.460345140884494</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.810997378644712</v>
+        <v>5.800467550519032</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240920.xlsx
+++ b/tame_output/ON/bt/strategyON_20240920.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>59.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>119.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>100.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>180.8%</t>
+          <t>194.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.0%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-591.6%</t>
+          <t>-588.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-55.8%</t>
+          <t>-54.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.3%</t>
+          <t>113.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.2%</t>
+          <t>-320.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-80.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.3%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>120.7%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>134.0%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2092"/>
+  <dimension ref="A1:G2093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.929162138771642</v>
+        <v>-2.95866307850059</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.028475826392619</v>
+        <v>2.016675450501039</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9937676410940548</v>
+        <v>0.9820880170877296</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.796757690871456</v>
+        <v>3.789749916467661</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.037462800641762</v>
+        <v>-3.06696374037071</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.998228968510489</v>
+        <v>1.98642859261891</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9937676410940548</v>
+        <v>0.9820880170877296</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.809831097737375</v>
+        <v>3.80282332333358</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.055266772362506</v>
+        <v>-3.084767712091454</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.983112576605132</v>
+        <v>1.971312200713553</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9232330181888537</v>
+        <v>0.9115533941825285</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.759515520777194</v>
+        <v>3.752507746373399</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.083167559471979</v>
+        <v>-3.112668499200927</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.970476302888344</v>
+        <v>1.958675926996765</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8886360940459189</v>
+        <v>0.8769564700395936</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.737281407418435</v>
+        <v>3.73027363301464</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.205693662174873</v>
+        <v>-3.23519460190382</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.918230305784386</v>
+        <v>1.906429929892806</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.766109991343025</v>
+        <v>0.7544303673366998</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.660530189773898</v>
+        <v>3.653522415370103</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.436208158360461</v>
+        <v>-3.465709098089409</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.892730466900654</v>
+        <v>1.880930091009075</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5355954951574363</v>
+        <v>0.523915871151111</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.588927451653048</v>
+        <v>3.581919677249253</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.784953243584905</v>
+        <v>-3.814454183313853</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.893544151812724</v>
+        <v>1.881743775921144</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4268475412385385</v>
+        <v>0.4151679172322132</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.663990398303557</v>
+        <v>3.656982623899762</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.938939661361045</v>
+        <v>-3.968440601089993</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.900929853847907</v>
+        <v>1.889129477956328</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4268475412385385</v>
+        <v>0.4151679172322132</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.732970667449197</v>
+        <v>3.725962893045402</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.143539096224054</v>
+        <v>-4.173040035953002</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.805141282022825</v>
+        <v>1.793340906131246</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4268475412385385</v>
+        <v>0.4151679172322132</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.719021869569318</v>
+        <v>3.712014095165522</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.396014250231778</v>
+        <v>-4.425515189960726</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.716021709475149</v>
+        <v>1.70422133358357</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4268475412385385</v>
+        <v>0.4151679172322132</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.730892358624732</v>
+        <v>3.723884584220936</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.688910006711191</v>
+        <v>-4.718410946440138</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.600073941402328</v>
+        <v>1.588273565510748</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4268475412385385</v>
+        <v>0.4151679172322132</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.732102893143675</v>
+        <v>3.72509511873988</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.875574134845999</v>
+        <v>-4.905075074574946</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.529530032375726</v>
+        <v>1.517729656484147</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4001085704139786</v>
+        <v>0.3884289464076534</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.720181252876261</v>
+        <v>3.713173478472465</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.021594821759961</v>
+        <v>-5.051095761488908</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.46619961034633</v>
+        <v>1.454399234454751</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3910254786201217</v>
+        <v>0.3793458546137964</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.709809250536136</v>
+        <v>3.702801476132341</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.113308830869546</v>
+        <v>-5.142809770598493</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.591718063401541</v>
+        <v>1.579917687509961</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3910254786201217</v>
+        <v>0.3793458546137964</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.87201330723518</v>
+        <v>3.865005532831385</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.144960489929515</v>
+        <v>-5.174461429658463</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.573904037741367</v>
+        <v>1.562103661849788</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3858570213756815</v>
+        <v>0.3741773973693562</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.86375887085233</v>
+        <v>3.856751096448535</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.214026544502452</v>
+        <v>-5.243527484231399</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.556507033480683</v>
+        <v>1.544706657589105</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3234861438820714</v>
+        <v>0.3118065198757461</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.836565761924655</v>
+        <v>3.82955798752086</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.316002666750859</v>
+        <v>-5.345503606479807</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.524642223037223</v>
+        <v>1.512841847145644</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2215100216336638</v>
+        <v>0.2098303976273386</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.784305727031513</v>
+        <v>3.777297952627718</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.316212433604777</v>
+        <v>-5.235497323002585</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.516711203539831</v>
+        <v>1.548997247780708</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2267224964254927</v>
+        <v>0.2330349695446138</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.779586099150786</v>
+        <v>3.783373583022259</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.173152857863851</v>
+        <v>-5.092437747261659</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.578185044558176</v>
+        <v>1.610471088799053</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.234735923015472</v>
+        <v>0.2410483961345931</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.788644165826748</v>
+        <v>3.79243164969822</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.871706132392013</v>
+        <v>-4.790991021789822</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.706024617629447</v>
+        <v>1.738310661870324</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5361826484873092</v>
+        <v>0.5424951216064303</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.976773083992386</v>
+        <v>3.980560567863859</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.896296376627197</v>
+        <v>-4.815581266025005</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.697159697688084</v>
+        <v>1.729445741928961</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5361826484873092</v>
+        <v>0.5424951216064303</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.977744261745096</v>
+        <v>3.98153174561657</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.845258000620677</v>
+        <v>-4.764542890018485</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.718417952470447</v>
+        <v>1.750703996711324</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5361826484873092</v>
+        <v>0.5424951216064303</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.978587166124852</v>
+        <v>3.982374649996325</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.804118705754046</v>
+        <v>-4.723403595151854</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.753911769291245</v>
+        <v>1.786197813532122</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.57732194335394</v>
+        <v>0.5836344164730611</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.022308841918976</v>
+        <v>4.026096325790449</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.707483793735406</v>
+        <v>-4.626768683133214</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.608749730222636</v>
+        <v>1.641035774463513</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.67395685537258</v>
+        <v>0.6802693284917011</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.896473785254094</v>
+        <v>3.900261269125567</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.638445782786938</v>
+        <v>-4.557730672184746</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.639866978675987</v>
+        <v>1.672153022916864</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7429948663210481</v>
+        <v>0.7493073394401691</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.94139863589714</v>
+        <v>3.945186119768612</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.473949448595977</v>
+        <v>-4.393234337993785</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.690092331428454</v>
+        <v>1.722378375669331</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9074912005120099</v>
+        <v>0.913803673631131</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.024523255487799</v>
+        <v>4.028310739359272</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.396850847054104</v>
+        <v>-4.377212243741891</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.720119482481633</v>
+        <v>1.727974923806519</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9074912005120099</v>
+        <v>0.913803673631131</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.023710965924229</v>
+        <v>4.027498449795702</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.407236041943993</v>
+        <v>-4.38759743863178</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.72583418365075</v>
+        <v>1.733689624975635</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8971060056221206</v>
+        <v>0.9034184787412417</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.027348628115368</v>
+        <v>4.03113611198684</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.425824200666218</v>
+        <v>-4.406185597354005</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.789235925938285</v>
+        <v>1.79709136726317</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8785178468998953</v>
+        <v>0.8848303200190164</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.087032738658458</v>
+        <v>4.09082022252993</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.426122747362254</v>
+        <v>-4.406484144050041</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.785985518078169</v>
+        <v>1.793840959403054</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8782193002038594</v>
+        <v>0.8845317733229805</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.083722621459135</v>
+        <v>4.087510105330607</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.325299613671826</v>
+        <v>-4.305661010359613</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.830845666493732</v>
+        <v>1.838701107818617</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8906835156882132</v>
+        <v>0.8969959888073343</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.095732045689139</v>
+        <v>4.099519529560611</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.134518252919419</v>
+        <v>-4.114879649607206</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.907287464273238</v>
+        <v>1.915142905598124</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.081464876440621</v>
+        <v>1.087777349559742</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.210330115619126</v>
+        <v>4.214117599490599</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.027554895069997</v>
+        <v>-4.007916291757784</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.929909653150603</v>
+        <v>1.937765094475489</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.139929484400422</v>
+        <v>1.146241957519543</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.225245726132604</v>
+        <v>4.229033210004077</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.972224307168235</v>
+        <v>-3.952585703856022</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.987008824923366</v>
+        <v>1.994864266248252</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.195260072302184</v>
+        <v>1.201572545421305</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.293411015485719</v>
+        <v>4.297198499357192</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.960170180255272</v>
+        <v>-3.940531576943059</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.985517043589989</v>
+        <v>1.993372484914874</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.207314199215147</v>
+        <v>1.213626672334268</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.294330059534935</v>
+        <v>4.298117543406407</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.001325299823494</v>
+        <v>-3.98168669651128</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.970935625946837</v>
+        <v>1.978791067271722</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.166159079646926</v>
+        <v>1.172471552766047</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.271517617978138</v>
+        <v>4.275305101849611</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.933276737131964</v>
+        <v>-3.91363813381975</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.011006076901332</v>
+        <v>2.018861518226217</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.234207642338456</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.325197781470939</v>
+        <v>4.328985265342411</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.164877130301464</v>
+        <v>-4.145238526989251</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.938568589807125</v>
+        <v>1.94642403113201</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.234207642338456</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.345400451644533</v>
+        <v>4.349187935516005</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.214928675830684</v>
+        <v>-4.195290072518471</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.902154207662319</v>
+        <v>1.910009648987204</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.234207642338456</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.329006687711415</v>
+        <v>4.332794171582887</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.390035508407129</v>
+        <v>-4.370396905094916</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.792363388225208</v>
+        <v>1.800218829550093</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.234207642338456</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.289258601304882</v>
+        <v>4.293046085176353</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.193935354976606</v>
+        <v>-4.174296751664393</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.877826068594357</v>
+        <v>1.885681509919242</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.430307795768979</v>
+        <v>1.4366202688881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.413941312360135</v>
+        <v>4.417728796231607</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.040909962863322</v>
+        <v>-4.021271359551108</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.038207225012576</v>
+        <v>2.046062666337461</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.583333187882263</v>
+        <v>1.589645661001384</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.60492754720101</v>
+        <v>4.608715031072482</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.069217276736592</v>
+        <v>-4.049578673424379</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.21435052437156</v>
+        <v>2.222205965696445</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.583333187882263</v>
+        <v>1.589645661001384</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.792393772109302</v>
+        <v>4.796181255980775</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.235810501850114</v>
+        <v>-4.216171898537901</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.117116185680234</v>
+        <v>2.124971627005119</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.41673996276874</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.661840788395271</v>
+        <v>4.665628272266744</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.212774708488548</v>
+        <v>-4.193136105176335</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.130006905686578</v>
+        <v>2.137862347011463</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.41673996276874</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.665517191056989</v>
+        <v>4.669304674928462</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.183528728032852</v>
+        <v>-4.163890124720639</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.139323352992351</v>
+        <v>2.147178794317237</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.41673996276874</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.663135246180484</v>
+        <v>4.666922730051957</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.290454275910703</v>
+        <v>-4.27081567259849</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.093846372998846</v>
+        <v>2.101701814323731</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.309814414890889</v>
+        <v>1.31612688801001</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.596273156611409</v>
+        <v>4.600060640482882</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.435472834417951</v>
+        <v>-4.415834231105738</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.037267751739181</v>
+        <v>2.045123193064066</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.16479585638364</v>
+        <v>1.171108329502762</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.510690823650294</v>
+        <v>4.514478307521767</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.553814600202669</v>
+        <v>-4.534175996890456</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.089862284683047</v>
+        <v>2.097717726007932</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.175481894946531</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.617033686045781</v>
+        <v>4.620821169917254</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.605225022523377</v>
+        <v>-4.585586419211164</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.067083812880703</v>
+        <v>2.074939254205588</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.175481894946531</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.61481938317172</v>
+        <v>4.618606867043193</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.684644473731129</v>
+        <v>-4.665005870418915</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.035219160471891</v>
+        <v>2.043074601796777</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.175481894946531</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.61472251124601</v>
+        <v>4.618509995117482</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.780107471648346</v>
+        <v>-4.760468868336133</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.997027854863047</v>
+        <v>2.004883296187932</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.175481894946531</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.614716404804052</v>
+        <v>4.618503888675525</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.715731560797631</v>
+        <v>-4.696092957485418</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.020874615765944</v>
+        <v>2.028730057090829</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.239857805797246</v>
+        <v>1.246170278916367</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.651438347877092</v>
+        <v>4.655225831748565</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.771100722929825</v>
+        <v>-4.751462119617612</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.004460768660793</v>
+        <v>2.012316209985678</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.239857805797246</v>
+        <v>1.246170278916367</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.657172165624819</v>
+        <v>4.660959649496291</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.816538502760652</v>
+        <v>-4.796899899448439</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.985824020071394</v>
+        <v>1.99367946139628</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.197012815119086</v>
+        <v>1.203325288238207</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.631003534560856</v>
+        <v>4.634791018432328</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.728331668613074</v>
+        <v>-4.708693065300861</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.040981146580744</v>
+        <v>2.04883658790563</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.197012815119086</v>
+        <v>1.203325288238207</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.650877927411174</v>
+        <v>4.654665411282647</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.622296673407765</v>
+        <v>-4.602658070095552</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.067095845187596</v>
+        <v>2.074951286512481</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.197012815119086</v>
+        <v>1.203325288238207</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.634578627935902</v>
+        <v>4.638366111807374</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.43908501027467</v>
+        <v>-4.419446406962456</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.14281145990488</v>
+        <v>2.150666901229765</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.197012815119086</v>
+        <v>1.203325288238207</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.637009577399947</v>
+        <v>4.64079706127142</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.367363563260819</v>
+        <v>-4.347724959948605</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.13729122455831</v>
+        <v>2.145146665883195</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.268734262132937</v>
+        <v>1.275046735252058</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.645833631456147</v>
+        <v>4.64962111532762</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.344990537653112</v>
+        <v>-4.325351934340899</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.093156180722564</v>
+        <v>2.101011622047449</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.279990013245838</v>
+        <v>1.286302486364959</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.59950282804506</v>
+        <v>4.603290311916533</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.378006833563857</v>
+        <v>-4.358368230251644</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.265147867243621</v>
+        <v>2.273003308568506</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.210552636579087</v>
+        <v>1.216865109698208</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.743038606930364</v>
+        <v>4.746826090801837</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.366479197914249</v>
+        <v>-4.346840594602035</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.261680147331714</v>
+        <v>2.269535588656599</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.269553294780449</v>
+        <v>1.27586576789957</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.770360227679431</v>
+        <v>4.774147711550904</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.415892609334863</v>
+        <v>-4.444182095944404</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.245582895285256</v>
+        <v>2.23426710064144</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.252596831038402</v>
+        <v>1.231445585734082</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.763854461955991</v>
+        <v>4.751163714773399</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.50174863867483</v>
+        <v>-4.530038125284371</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.212491565742108</v>
+        <v>2.201175771098292</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.210220761812267</v>
+        <v>1.189069516507947</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.739679902613148</v>
+        <v>4.726989155430556</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.510585436090949</v>
+        <v>-4.53887492270049</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.191376048596162</v>
+        <v>2.180060253952345</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.202778589170916</v>
+        <v>1.181627343866596</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.71763380084884</v>
+        <v>4.704943053666248</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.601967998656407</v>
+        <v>-4.630257485265949</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.164987534615028</v>
+        <v>2.153671739971212</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.166213704451572</v>
+        <v>1.145062459147252</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.705859381062282</v>
+        <v>4.69316863387969</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.590261280669401</v>
+        <v>-4.618550767278943</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.271798479634098</v>
+        <v>2.260482684990281</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.177920422438578</v>
+        <v>1.156769177134258</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.815011669678753</v>
+        <v>4.802320922496161</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.490597776585739</v>
+        <v>-4.51888726319528</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.314696219998968</v>
+        <v>2.303380425355151</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.241107505642265</v>
+        <v>1.219956260337945</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.855956258332371</v>
+        <v>4.843265511149778</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.500913874752091</v>
+        <v>-4.529203361361632</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.523474614010485</v>
+        <v>2.512158819366668</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.241107505642265</v>
+        <v>1.219956260337945</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.068861091610429</v>
+        <v>5.056170344427836</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.500819906734718</v>
+        <v>-4.529109393344259</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.522690868129524</v>
+        <v>2.511375073485707</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.241477366989583</v>
+        <v>1.220326121685263</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.068261675330909</v>
+        <v>5.055570928148317</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.508038730934563</v>
+        <v>-4.536328217544104</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.51403532439394</v>
+        <v>2.502719529750123</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.241477366989583</v>
+        <v>1.220326121685263</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.062493661275263</v>
+        <v>5.049802914092671</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.507090307816524</v>
+        <v>-4.535379794426065</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.514414693641155</v>
+        <v>2.503098898997338</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.241477366989583</v>
+        <v>1.220326121685263</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.062493661275263</v>
+        <v>5.049802914092671</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.664158766072148</v>
+        <v>-4.69244825268169</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.464314918319998</v>
+        <v>2.452999123676181</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.241477366989583</v>
+        <v>1.220326121685263</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.075221269256355</v>
+        <v>5.062530522073763</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.658166519283337</v>
+        <v>-4.686456005892878</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.46865781545991</v>
+        <v>2.457342020816093</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.241477366989583</v>
+        <v>1.220326121685263</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.077167267680743</v>
+        <v>5.06447652049815</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.569608558152569</v>
+        <v>-4.59789804476211</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.497735135929986</v>
+        <v>2.486419341286169</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.241477366989583</v>
+        <v>1.220326121685263</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.070821403698512</v>
+        <v>5.058130656515919</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.551849480649495</v>
+        <v>-4.580138967259036</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.504147444370211</v>
+        <v>2.492831649726394</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.241477366989583</v>
+        <v>1.220326121685263</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.070130081137507</v>
+        <v>5.057439333954915</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.452219329600427</v>
+        <v>-4.480508816209968</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.556781690698425</v>
+        <v>2.545465896054608</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.34110751803865</v>
+        <v>1.31995627273433</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.142690357675535</v>
+        <v>5.129999610492942</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.501618838289438</v>
+        <v>-4.52990832489898</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.726176152721547</v>
+        <v>2.71486035807773</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.351366351470395</v>
+        <v>1.330215106166075</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.337999923233308</v>
+        <v>5.325309176050715</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.294934364647062</v>
+        <v>-4.323223851256603</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.796038615281359</v>
+        <v>2.784722820637543</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.558050825112771</v>
+        <v>1.536899579808451</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.449199280521595</v>
+        <v>5.436508533339003</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.329091259644589</v>
+        <v>-4.35738074625413</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.784377370936454</v>
+        <v>2.773061576292637</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.474467055571958</v>
+        <v>1.453315810267638</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.401050532451213</v>
+        <v>5.38835978526862</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.236501780583132</v>
+        <v>-4.264791267192673</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.174910276550704</v>
+        <v>3.163594481906888</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.474467055571958</v>
+        <v>1.453315810267638</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.75454764644088</v>
+        <v>5.741856899258288</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.296390408406682</v>
+        <v>-4.324679895016224</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.155517936988387</v>
+        <v>3.144202142344571</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.460345140884494</v>
+        <v>1.439193895580174</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.750637609195504</v>
+        <v>5.737946862012913</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,45 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.860249295492581</v>
+        <v>3.835202441103564</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.300261802518784</v>
+        <v>-4.272463585219882</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.203799320667074</v>
+        <v>3.214918607586635</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.460345140884494</v>
+        <v>1.439193895580174</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.800467550519032</v>
+        <v>5.78777680333644</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="2" t="n">
+        <v>45555</v>
+      </c>
+      <c r="B2093" t="n">
+        <v>3.8801626440462</v>
+      </c>
+      <c r="C2093" t="n">
+        <v>5.065166317142233</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>-4.272463585219882</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>3.214918607586635</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>1.439193895580174</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>5.058230114128601</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240920.xlsx
+++ b/tame_output/ON/bt/strategyON_20240920.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-70.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-588.8%</t>
+          <t>-582.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-54.7%</t>
+          <t>-52.3%</t>
         </is>
       </c>
     </row>
@@ -48379,10 +48379,10 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.377212243741891</v>
+        <v>-4.316135736451912</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.727974923806519</v>
+        <v>1.75240552672251</v>
       </c>
       <c r="F2036" t="n">
         <v>0.913803673631131</v>
@@ -48402,10 +48402,10 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.38759743863178</v>
+        <v>-4.326520931341801</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.733689624975635</v>
+        <v>1.758120227891627</v>
       </c>
       <c r="F2037" t="n">
         <v>0.9034184787412417</v>
@@ -48425,10 +48425,10 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.406185597354005</v>
+        <v>-4.345109090064026</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.79709136726317</v>
+        <v>1.821521970179162</v>
       </c>
       <c r="F2038" t="n">
         <v>0.8848303200190164</v>
@@ -48448,10 +48448,10 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.406484144050041</v>
+        <v>-4.345407636760062</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.793840959403054</v>
+        <v>1.818271562319046</v>
       </c>
       <c r="F2039" t="n">
         <v>0.8845317733229805</v>
@@ -48471,10 +48471,10 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.305661010359613</v>
+        <v>-4.244584503069635</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.838701107818617</v>
+        <v>1.863131710734609</v>
       </c>
       <c r="F2040" t="n">
         <v>0.8969959888073343</v>
@@ -48494,10 +48494,10 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.114879649607206</v>
+        <v>-4.053803142317227</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.915142905598124</v>
+        <v>1.939573508514115</v>
       </c>
       <c r="F2041" t="n">
         <v>1.087777349559742</v>
@@ -48517,10 +48517,10 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.007916291757784</v>
+        <v>-3.946839784467805</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.937765094475489</v>
+        <v>1.96219569739148</v>
       </c>
       <c r="F2042" t="n">
         <v>1.146241957519543</v>
@@ -48540,10 +48540,10 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.952585703856022</v>
+        <v>-3.891509196566043</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.994864266248252</v>
+        <v>2.019294869164243</v>
       </c>
       <c r="F2043" t="n">
         <v>1.201572545421305</v>
@@ -48563,10 +48563,10 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.940531576943059</v>
+        <v>-3.87945506965308</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.993372484914874</v>
+        <v>2.017803087830866</v>
       </c>
       <c r="F2044" t="n">
         <v>1.213626672334268</v>
@@ -48586,10 +48586,10 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.98168669651128</v>
+        <v>-3.920610189221301</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.978791067271722</v>
+        <v>2.003221670187714</v>
       </c>
       <c r="F2045" t="n">
         <v>1.172471552766047</v>
@@ -48609,10 +48609,10 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.91363813381975</v>
+        <v>-3.852561626529771</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.018861518226217</v>
+        <v>2.043292121142208</v>
       </c>
       <c r="F2046" t="n">
         <v>1.240520115457577</v>
@@ -48632,10 +48632,10 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.145238526989251</v>
+        <v>-4.084162019699273</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.94642403113201</v>
+        <v>1.970854634048002</v>
       </c>
       <c r="F2047" t="n">
         <v>1.240520115457577</v>
@@ -48655,10 +48655,10 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.195290072518471</v>
+        <v>-4.134213565228492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.910009648987204</v>
+        <v>1.934440251903196</v>
       </c>
       <c r="F2048" t="n">
         <v>1.240520115457577</v>
@@ -48678,10 +48678,10 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.370396905094916</v>
+        <v>-4.309320397804937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.800218829550093</v>
+        <v>1.824649432466085</v>
       </c>
       <c r="F2049" t="n">
         <v>1.240520115457577</v>
@@ -48701,10 +48701,10 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.174296751664393</v>
+        <v>-4.113220244374414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.885681509919242</v>
+        <v>1.910112112835234</v>
       </c>
       <c r="F2050" t="n">
         <v>1.4366202688881</v>
@@ -48724,10 +48724,10 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.021271359551108</v>
+        <v>-3.96019485226113</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.046062666337461</v>
+        <v>2.070493269253452</v>
       </c>
       <c r="F2051" t="n">
         <v>1.589645661001384</v>
@@ -48747,10 +48747,10 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.049578673424379</v>
+        <v>-3.9885021661344</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.222205965696445</v>
+        <v>2.246636568612437</v>
       </c>
       <c r="F2052" t="n">
         <v>1.589645661001384</v>
@@ -48770,10 +48770,10 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.216171898537901</v>
+        <v>-4.155095391247922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.124971627005119</v>
+        <v>2.14940222992111</v>
       </c>
       <c r="F2053" t="n">
         <v>1.423052435887861</v>
@@ -48793,10 +48793,10 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.193136105176335</v>
+        <v>-4.132059597886356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.137862347011463</v>
+        <v>2.162292949927454</v>
       </c>
       <c r="F2054" t="n">
         <v>1.423052435887861</v>
@@ -48816,10 +48816,10 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.163890124720639</v>
+        <v>-4.10281361743066</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.147178794317237</v>
+        <v>2.171609397233228</v>
       </c>
       <c r="F2055" t="n">
         <v>1.423052435887861</v>
@@ -48839,10 +48839,10 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.27081567259849</v>
+        <v>-4.209739165308511</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.101701814323731</v>
+        <v>2.126132417239723</v>
       </c>
       <c r="F2056" t="n">
         <v>1.31612688801001</v>
@@ -48862,10 +48862,10 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.415834231105738</v>
+        <v>-4.35475772381576</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.045123193064066</v>
+        <v>2.069553795980058</v>
       </c>
       <c r="F2057" t="n">
         <v>1.171108329502762</v>
@@ -48885,10 +48885,10 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.534175996890456</v>
+        <v>-4.473099489600477</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.097717726007932</v>
+        <v>2.122148328923924</v>
       </c>
       <c r="F2058" t="n">
         <v>1.181794368065652</v>
@@ -48908,10 +48908,10 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.585586419211164</v>
+        <v>-4.524509911921185</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.074939254205588</v>
+        <v>2.099369857121579</v>
       </c>
       <c r="F2059" t="n">
         <v>1.181794368065652</v>
@@ -48931,10 +48931,10 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.665005870418915</v>
+        <v>-4.603929363128937</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.043074601796777</v>
+        <v>2.067505204712768</v>
       </c>
       <c r="F2060" t="n">
         <v>1.181794368065652</v>
@@ -48954,10 +48954,10 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.760468868336133</v>
+        <v>-4.699392361046154</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.004883296187932</v>
+        <v>2.029313899103924</v>
       </c>
       <c r="F2061" t="n">
         <v>1.181794368065652</v>
@@ -48977,10 +48977,10 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.696092957485418</v>
+        <v>-4.635016450195439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.028730057090829</v>
+        <v>2.053160660006821</v>
       </c>
       <c r="F2062" t="n">
         <v>1.246170278916367</v>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.751462119617612</v>
+        <v>-4.690385612327633</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.012316209985678</v>
+        <v>2.036746812901669</v>
       </c>
       <c r="F2063" t="n">
         <v>1.246170278916367</v>
@@ -49023,10 +49023,10 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.796899899448439</v>
+        <v>-4.73582339215846</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.99367946139628</v>
+        <v>2.018110064312271</v>
       </c>
       <c r="F2064" t="n">
         <v>1.203325288238207</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.708693065300861</v>
+        <v>-4.647616558010882</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.04883658790563</v>
+        <v>2.073267190821621</v>
       </c>
       <c r="F2065" t="n">
         <v>1.203325288238207</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.602658070095552</v>
+        <v>-4.541581562805573</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.074951286512481</v>
+        <v>2.099381889428473</v>
       </c>
       <c r="F2066" t="n">
         <v>1.203325288238207</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.419446406962456</v>
+        <v>-4.358369899672478</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.150666901229765</v>
+        <v>2.175097504145756</v>
       </c>
       <c r="F2067" t="n">
         <v>1.203325288238207</v>
@@ -49115,10 +49115,10 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.347724959948605</v>
+        <v>-4.286648452658627</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.145146665883195</v>
+        <v>2.169577268799187</v>
       </c>
       <c r="F2068" t="n">
         <v>1.275046735252058</v>
@@ -49138,10 +49138,10 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.325351934340899</v>
+        <v>-4.26427542705092</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.101011622047449</v>
+        <v>2.125442224963441</v>
       </c>
       <c r="F2069" t="n">
         <v>1.286302486364959</v>
@@ -49161,10 +49161,10 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.358368230251644</v>
+        <v>-4.297291722961665</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.273003308568506</v>
+        <v>2.297433911484498</v>
       </c>
       <c r="F2070" t="n">
         <v>1.216865109698208</v>
@@ -49184,10 +49184,10 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.346840594602035</v>
+        <v>-4.285764087312057</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.269535588656599</v>
+        <v>2.29396619157259</v>
       </c>
       <c r="F2071" t="n">
         <v>1.27586576789957</v>
@@ -49207,10 +49207,10 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.444182095944404</v>
+        <v>-4.383105588654425</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.23426710064144</v>
+        <v>2.258697703557432</v>
       </c>
       <c r="F2072" t="n">
         <v>1.231445585734082</v>
@@ -49230,10 +49230,10 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.530038125284371</v>
+        <v>-4.468961617994392</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.201175771098292</v>
+        <v>2.225606374014283</v>
       </c>
       <c r="F2073" t="n">
         <v>1.189069516507947</v>
@@ -49253,10 +49253,10 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.53887492270049</v>
+        <v>-4.477798415410511</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.180060253952345</v>
+        <v>2.204490856868337</v>
       </c>
       <c r="F2074" t="n">
         <v>1.181627343866596</v>
@@ -49276,10 +49276,10 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.630257485265949</v>
+        <v>-4.56918097797597</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.153671739971212</v>
+        <v>2.178102342887203</v>
       </c>
       <c r="F2075" t="n">
         <v>1.145062459147252</v>
@@ -49299,10 +49299,10 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.618550767278943</v>
+        <v>-4.557474259988964</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.260482684990281</v>
+        <v>2.284913287906273</v>
       </c>
       <c r="F2076" t="n">
         <v>1.156769177134258</v>
@@ -49322,10 +49322,10 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.51888726319528</v>
+        <v>-4.457810755905301</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.303380425355151</v>
+        <v>2.327811028271142</v>
       </c>
       <c r="F2077" t="n">
         <v>1.219956260337945</v>
@@ -49345,10 +49345,10 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.529203361361632</v>
+        <v>-4.468126854071653</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.512158819366668</v>
+        <v>2.53658942228266</v>
       </c>
       <c r="F2078" t="n">
         <v>1.219956260337945</v>
@@ -49368,10 +49368,10 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.529109393344259</v>
+        <v>-4.468032886054281</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.511375073485707</v>
+        <v>2.535805676401699</v>
       </c>
       <c r="F2079" t="n">
         <v>1.220326121685263</v>
@@ -49391,10 +49391,10 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.536328217544104</v>
+        <v>-4.475251710254125</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.502719529750123</v>
+        <v>2.527150132666115</v>
       </c>
       <c r="F2080" t="n">
         <v>1.220326121685263</v>
@@ -49414,10 +49414,10 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.535379794426065</v>
+        <v>-4.474303287136086</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.503098898997338</v>
+        <v>2.52752950191333</v>
       </c>
       <c r="F2081" t="n">
         <v>1.220326121685263</v>
@@ -49437,10 +49437,10 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.69244825268169</v>
+        <v>-4.631371745391711</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.452999123676181</v>
+        <v>2.477429726592173</v>
       </c>
       <c r="F2082" t="n">
         <v>1.220326121685263</v>
@@ -49460,10 +49460,10 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.686456005892878</v>
+        <v>-4.625379498602899</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.457342020816093</v>
+        <v>2.481772623732085</v>
       </c>
       <c r="F2083" t="n">
         <v>1.220326121685263</v>
@@ -49483,10 +49483,10 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.59789804476211</v>
+        <v>-4.536821537472131</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.486419341286169</v>
+        <v>2.510849944202161</v>
       </c>
       <c r="F2084" t="n">
         <v>1.220326121685263</v>
@@ -49506,10 +49506,10 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.580138967259036</v>
+        <v>-4.519062459969057</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.492831649726394</v>
+        <v>2.517262252642386</v>
       </c>
       <c r="F2085" t="n">
         <v>1.220326121685263</v>
@@ -49529,10 +49529,10 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.480508816209968</v>
+        <v>-4.41943230891999</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.545465896054608</v>
+        <v>2.5698964989706</v>
       </c>
       <c r="F2086" t="n">
         <v>1.31995627273433</v>
@@ -49552,10 +49552,10 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.52990832489898</v>
+        <v>-4.468831817609001</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.71486035807773</v>
+        <v>2.739290960993722</v>
       </c>
       <c r="F2087" t="n">
         <v>1.330215106166075</v>
@@ -49575,10 +49575,10 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.323223851256603</v>
+        <v>-4.262147343966625</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.784722820637543</v>
+        <v>2.809153423553535</v>
       </c>
       <c r="F2088" t="n">
         <v>1.536899579808451</v>
@@ -49598,10 +49598,10 @@
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.35738074625413</v>
+        <v>-4.296304238964151</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.773061576292637</v>
+        <v>2.797492179208629</v>
       </c>
       <c r="F2089" t="n">
         <v>1.453315810267638</v>
@@ -49621,10 +49621,10 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.264791267192673</v>
+        <v>-4.203714759902694</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.163594481906888</v>
+        <v>3.188025084822879</v>
       </c>
       <c r="F2090" t="n">
         <v>1.453315810267638</v>
@@ -49644,10 +49644,10 @@
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.324679895016224</v>
+        <v>-4.263603387726245</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.144202142344571</v>
+        <v>3.168632745260562</v>
       </c>
       <c r="F2091" t="n">
         <v>1.439193895580174</v>
@@ -49661,16 +49661,16 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103564</v>
+        <v>3.835202441103563</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.272463585219882</v>
+        <v>-4.211387077929903</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.214918607586635</v>
+        <v>3.239349210502626</v>
       </c>
       <c r="F2092" t="n">
         <v>1.439193895580174</v>
@@ -49687,19 +49687,19 @@
         <v>3.8801626440462</v>
       </c>
       <c r="C2093" t="n">
-        <v>5.065166317142233</v>
+        <v>5.065166317142232</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.272463585219882</v>
+        <v>-4.211387077929903</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.214918607586635</v>
+        <v>3.239349210502626</v>
       </c>
       <c r="F2093" t="n">
         <v>1.439193895580174</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.058230114128601</v>
+        <v>5.0582301141286</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240920.xlsx
+++ b/tame_output/ON/bt/strategyON_20240920.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>119.7%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>100.5%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>194.9%</t>
+          <t>184.8%</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.6%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.6%</t>
+          <t>-321.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
     </row>
@@ -49684,10 +49684,10 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.8801626440462</v>
+        <v>3.791974059255759</v>
       </c>
       <c r="C2093" t="n">
-        <v>5.065166317142232</v>
+        <v>4.964138582160562</v>
       </c>
       <c r="D2093" t="n">
         <v>-4.211387077929903</v>
@@ -49699,7 +49699,7 @@
         <v>1.439193895580174</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.0582301141286</v>
+        <v>4.95720237914693</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240920.xlsx
+++ b/tame_output/ON/bt/strategyON_20240920.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>114.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>184.8%</t>
+          <t>180.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-582.7%</t>
+          <t>-592.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-52.3%</t>
+          <t>-69.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.1%</t>
+          <t>-321.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-89.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
     </row>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635016450195439</v>
+        <v>-4.732299418466408</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053160660006821</v>
+        <v>2.014247472698433</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>1.148887310645399</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.596856050785984</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690385612327633</v>
+        <v>-4.787668580598601</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036746812901669</v>
+        <v>1.997833625593282</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>1.148887310645399</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.602589868533711</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.73582339215846</v>
+        <v>-4.833106360429428</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.018110064312271</v>
+        <v>1.979196877003884</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.203325288238207</v>
+        <v>1.106042319967239</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.634791018432328</v>
+        <v>4.576421237469747</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.647616558010882</v>
+        <v>-4.74489952628185</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.073267190821621</v>
+        <v>2.034354003513234</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.203325288238207</v>
+        <v>1.106042319967239</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.654665411282647</v>
+        <v>4.596295630320066</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.541581562805573</v>
+        <v>-4.638864531076541</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.099381889428473</v>
+        <v>2.060468702120086</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.203325288238207</v>
+        <v>1.106042319967239</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.638366111807374</v>
+        <v>4.579996330844794</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.358369899672478</v>
+        <v>-4.455652867943446</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.175097504145756</v>
+        <v>2.136184316837369</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.203325288238207</v>
+        <v>1.106042319967239</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.64079706127142</v>
+        <v>4.582427280308839</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.286648452658627</v>
+        <v>-4.383931420929595</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.169577268799187</v>
+        <v>2.130664081490799</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.275046735252058</v>
+        <v>1.17776376698109</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.64962111532762</v>
+        <v>4.591251334365039</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.26427542705092</v>
+        <v>-4.361558395321889</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.125442224963441</v>
+        <v>2.086529037655053</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.286302486364959</v>
+        <v>1.189019518093991</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.603290311916533</v>
+        <v>4.544920530953952</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.297291722961665</v>
+        <v>-4.394574691232633</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.297433911484498</v>
+        <v>2.258520724176111</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.216865109698208</v>
+        <v>1.11958214142724</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.746826090801837</v>
+        <v>4.688456309839256</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.285764087312057</v>
+        <v>-4.383047055583025</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.29396619157259</v>
+        <v>2.255053004264203</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.27586576789957</v>
+        <v>1.178582799628602</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.774147711550904</v>
+        <v>4.715777930588323</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.383105588654425</v>
+        <v>-4.480388556925393</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.258697703557432</v>
+        <v>2.219784516249044</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.231445585734082</v>
+        <v>1.134162617463114</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.751163714773399</v>
+        <v>4.692793933810818</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.468961617994392</v>
+        <v>-4.56624458626536</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.225606374014283</v>
+        <v>2.186693186705896</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.189069516507947</v>
+        <v>1.091786548236979</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.726989155430556</v>
+        <v>4.668619374467975</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.477798415410511</v>
+        <v>-4.575081383681479</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.204490856868337</v>
+        <v>2.16557766955995</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.181627343866596</v>
+        <v>1.084344375595628</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.704943053666248</v>
+        <v>4.646573272703667</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.56918097797597</v>
+        <v>-4.666463946246938</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.178102342887203</v>
+        <v>2.139189155578816</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.145062459147252</v>
+        <v>1.047779490876283</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.69316863387969</v>
+        <v>4.634798852917109</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.557474259988964</v>
+        <v>-4.654757228259932</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.284913287906273</v>
+        <v>2.246000100597886</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.156769177134258</v>
+        <v>1.05948620886329</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.802320922496161</v>
+        <v>4.74395114153358</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.457810755905301</v>
+        <v>-4.555093724176269</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.327811028271142</v>
+        <v>2.288897840962755</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.219956260337945</v>
+        <v>1.122673292066976</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.843265511149778</v>
+        <v>4.784895730187197</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.189192607468328</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.468126854071653</v>
+        <v>-4.565409822342621</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.53658942228266</v>
+        <v>2.362672254217532</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.219956260337945</v>
+        <v>1.122673292066976</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.056170344427836</v>
+        <v>4.862796582708515</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.188371274380418</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.468032886054281</v>
+        <v>-4.565315854325249</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.535805676401699</v>
+        <v>2.361888508336571</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.220326121685263</v>
+        <v>1.123043153414294</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.055570928148317</v>
+        <v>4.862197166428995</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.182603260324772</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.475251710254125</v>
+        <v>-4.572534678525093</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.527150132666115</v>
+        <v>2.353232964600987</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.220326121685263</v>
+        <v>1.123043153414294</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.049802914092671</v>
+        <v>4.856429152373349</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.182603260324772</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.474303287136086</v>
+        <v>-4.571586255407055</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.52752950191333</v>
+        <v>2.353612333848202</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.220326121685263</v>
+        <v>1.123043153414294</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.049802914092671</v>
+        <v>4.856429152373349</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.195330868305864</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.631371745391711</v>
+        <v>-4.728654713662678</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.477429726592173</v>
+        <v>2.303512558527045</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.220326121685263</v>
+        <v>1.123043153414294</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.062530522073763</v>
+        <v>4.869156760354441</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.197276866730252</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.625379498602899</v>
+        <v>-4.722662466873866</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.481772623732085</v>
+        <v>2.307855455666957</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.220326121685263</v>
+        <v>1.123043153414294</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.06447652049815</v>
+        <v>4.871102758778829</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.19093100274802</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.536821537472131</v>
+        <v>-4.634104505743099</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.510849944202161</v>
+        <v>2.336932776137033</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.220326121685263</v>
+        <v>1.123043153414294</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.058130656515919</v>
+        <v>4.864756894796598</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.190239680187016</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.519062459969057</v>
+        <v>-4.616345428240025</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.517262252642386</v>
+        <v>2.343345084577258</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.220326121685263</v>
+        <v>1.123043153414294</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.057439333954915</v>
+        <v>4.864065572235593</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.203021866095603</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.41943230891999</v>
+        <v>-4.516715277190957</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.5698964989706</v>
+        <v>2.395979330905472</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.31995627273433</v>
+        <v>1.222673304463362</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.129999610492942</v>
+        <v>4.936625848773621</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.392176131594329</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.468831817609001</v>
+        <v>-4.566114785879968</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.739290960993722</v>
+        <v>2.565373792928594</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.330215106166075</v>
+        <v>1.232932137895107</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.325309176050715</v>
+        <v>5.131935414331394</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.379364804697191</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.262147343966625</v>
+        <v>-4.359430312237592</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.809153423553535</v>
+        <v>2.635236255488406</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.536899579808451</v>
+        <v>1.439616611537482</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.436508533339003</v>
+        <v>5.243134771619681</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.516370299108037</v>
+        <v>4.381366318351296</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.296304238964151</v>
+        <v>-4.393587207235118</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.797492179208629</v>
+        <v>2.623575011143501</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.453315810267638</v>
+        <v>1.35603284199667</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.38835978526862</v>
+        <v>5.194986023549299</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.869867413097705</v>
+        <v>4.734863432340964</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.203714759902694</v>
+        <v>-4.300997728173662</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.188025084822879</v>
+        <v>3.014107916757751</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.453315810267638</v>
+        <v>1.35603284199667</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.741856899258288</v>
+        <v>5.548483137538966</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.874430524664808</v>
+        <v>4.739426543908067</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.263603387726245</v>
+        <v>-4.360886355997212</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.168632745260562</v>
+        <v>2.994715577195434</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.439193895580174</v>
+        <v>1.341910927309205</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.737946862012913</v>
+        <v>5.54457310029359</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103563</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.924260465988335</v>
+        <v>4.789256485231594</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.211387077929903</v>
+        <v>-4.30867004620087</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.239349210502626</v>
+        <v>3.065432042437498</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.439193895580174</v>
+        <v>1.341910927309205</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.78777680333644</v>
+        <v>5.594403041617118</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.791974059255759</v>
+        <v>3.855626132491441</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.964138582160562</v>
+        <v>4.920534808601623</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.211387077929903</v>
+        <v>-4.30867004620087</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.239349210502626</v>
+        <v>3.065432042437498</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.439193895580174</v>
+        <v>1.341910927309205</v>
       </c>
       <c r="G2093" t="n">
-        <v>4.95720237914693</v>
+        <v>4.913598605587991</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240920.xlsx
+++ b/tame_output/ON/bt/strategyON_20240920.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>53.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.9%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>180.4%</t>
+          <t>179.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.2%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-592.4%</t>
+          <t>-582.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-69.7%</t>
+          <t>-53.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.2%</t>
+          <t>-320.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-89.8%</t>
+          <t>-70.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>133.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>137.2%</t>
         </is>
       </c>
     </row>
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.092437747261659</v>
+        <v>-5.185717071638896</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.610471088799053</v>
+        <v>1.573159359048158</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2410483961345931</v>
+        <v>0.2375293898156866</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.79243164969822</v>
+        <v>3.790320245906877</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.790991021789822</v>
+        <v>-4.884270346167058</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.738310661870324</v>
+        <v>1.700998932119429</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.5389761152875239</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.980560567863859</v>
+        <v>3.978449164072515</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.815581266025005</v>
+        <v>-4.908860590402242</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.729445741928961</v>
+        <v>1.692134012178066</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.5389761152875239</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.98153174561657</v>
+        <v>3.979420341825225</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.764542890018485</v>
+        <v>-4.857822214395722</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.750703996711324</v>
+        <v>1.71339226696043</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.5389761152875239</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.982374649996325</v>
+        <v>3.980263246204981</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.723403595151854</v>
+        <v>-4.816682919529091</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.786197813532122</v>
+        <v>1.748886083781227</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5836344164730611</v>
+        <v>0.5801154101541547</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.026096325790449</v>
+        <v>4.023984921999105</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.626768683133214</v>
+        <v>-4.720048007510451</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.641035774463513</v>
+        <v>1.603724044712618</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6802693284917011</v>
+        <v>0.6767503221727946</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.900261269125567</v>
+        <v>3.898149865334223</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.557730672184746</v>
+        <v>-4.651009996561983</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.672153022916864</v>
+        <v>1.634841293165969</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7493073394401691</v>
+        <v>0.7457883331212627</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.945186119768612</v>
+        <v>3.943074715977269</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.393234337993785</v>
+        <v>-4.486513662371022</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.722378375669331</v>
+        <v>1.685066645918436</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.913803673631131</v>
+        <v>0.9102846673122246</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.028310739359272</v>
+        <v>4.026199335567928</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.316135736451912</v>
+        <v>-4.409415060829149</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.75240552672251</v>
+        <v>1.715093796971615</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.913803673631131</v>
+        <v>0.9102846673122246</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.027498449795702</v>
+        <v>4.025387046004358</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.326520931341801</v>
+        <v>-4.419800255719038</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.758120227891627</v>
+        <v>1.720808498140732</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9034184787412417</v>
+        <v>0.8998994724223353</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.03113611198684</v>
+        <v>4.029024708195497</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.345109090064026</v>
+        <v>-4.438388414441263</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.821521970179162</v>
+        <v>1.784210240428267</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8848303200190164</v>
+        <v>0.8813113137001098</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.09082022252993</v>
+        <v>4.088708818738587</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.345407636760062</v>
+        <v>-4.438686961137299</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.818271562319046</v>
+        <v>1.780959832568151</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8845317733229805</v>
+        <v>0.8810127670040739</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.087510105330607</v>
+        <v>4.085398701539264</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.244584503069635</v>
+        <v>-4.337863827446871</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.863131710734609</v>
+        <v>1.825819980983714</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8969959888073343</v>
+        <v>0.8934769824884278</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.099519529560611</v>
+        <v>4.097408125769267</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.053803142317227</v>
+        <v>-4.147082466694464</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.939573508514115</v>
+        <v>1.90226177876322</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.087777349559742</v>
+        <v>1.084258343240835</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.214117599490599</v>
+        <v>4.212006195699255</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.946839784467805</v>
+        <v>-4.040119108845042</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.96219569739148</v>
+        <v>1.924883967640585</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.146241957519543</v>
+        <v>1.142722951200636</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.229033210004077</v>
+        <v>4.226921806212732</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.891509196566043</v>
+        <v>-3.98478852094328</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.019294869164243</v>
+        <v>1.981983139413348</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.201572545421305</v>
+        <v>1.198053539102399</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.297198499357192</v>
+        <v>4.295087095565848</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.87945506965308</v>
+        <v>-3.972734394030317</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.017803087830866</v>
+        <v>1.980491358079972</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.213626672334268</v>
+        <v>1.210107666015361</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.298117543406407</v>
+        <v>4.296006139615064</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.920610189221301</v>
+        <v>-4.013889513598539</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.003221670187714</v>
+        <v>1.965909940436819</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.172471552766047</v>
+        <v>1.16895254644714</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.275305101849611</v>
+        <v>4.273193698058266</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.852561626529771</v>
+        <v>-3.945840950907009</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.043292121142208</v>
+        <v>2.005980391391313</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>1.23700110913867</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.326873861551067</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.084162019699273</v>
+        <v>-4.177441344076509</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.970854634048002</v>
+        <v>1.933542904297107</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>1.23700110913867</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.347076531724661</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134213565228492</v>
+        <v>-4.227492889605729</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934440251903196</v>
+        <v>1.897128522152301</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>1.23700110913867</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.330682767791544</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309320397804937</v>
+        <v>-4.402599722182174</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824649432466085</v>
+        <v>1.78733770271519</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>1.23700110913867</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.29093468138501</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113220244374414</v>
+        <v>-4.206499568751651</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910112112835234</v>
+        <v>1.872800383084339</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.433101262569193</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.415617392440264</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96019485226113</v>
+        <v>-4.053474176638367</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070493269253452</v>
+        <v>2.033181539502557</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.586126654682477</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.606603627281139</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.9885021661344</v>
+        <v>-4.081781490511637</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246636568612437</v>
+        <v>2.209324838861542</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.586126654682477</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.794069852189431</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155095391247922</v>
+        <v>-4.248374715625159</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14940222992111</v>
+        <v>2.112090500170216</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.419533429568955</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.6635168684754</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132059597886356</v>
+        <v>-4.225338922263593</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.162292949927454</v>
+        <v>2.12498122017656</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.419533429568955</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.667193271137118</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.10281361743066</v>
+        <v>-4.196092941807897</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171609397233228</v>
+        <v>2.134297667482334</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.419533429568955</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.664811326260613</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.209739165308511</v>
+        <v>-4.303018489685748</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.126132417239723</v>
+        <v>2.088820687488828</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>1.312607881691104</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.597949236691537</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.35475772381576</v>
+        <v>-4.448037048192997</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069553795980058</v>
+        <v>2.032242066229163</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>1.167589323183855</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.512366903730423</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473099489600477</v>
+        <v>-4.566378813977714</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.122148328923924</v>
+        <v>2.084836599173029</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>1.178275361746745</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.61870976612591</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524509911921185</v>
+        <v>-4.617789236298422</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099369857121579</v>
+        <v>2.062058127370685</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>1.178275361746745</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.616495463251849</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603929363128937</v>
+        <v>-4.697208687506174</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067505204712768</v>
+        <v>2.030193474961873</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>1.178275361746745</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.616398591326139</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699392361046154</v>
+        <v>-4.792671685423391</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.029313899103924</v>
+        <v>1.992002169353029</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>1.178275361746745</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.616392484884181</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217999</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.732299418466408</v>
+        <v>-4.728295774572676</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.014247472698433</v>
+        <v>2.015848930255926</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.148887310645399</v>
+        <v>1.24265127259746</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.596856050785984</v>
+        <v>4.65311442795722</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353534</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.787668580598601</v>
+        <v>-4.78366493670487</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.997833625593282</v>
+        <v>1.999435083150775</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.148887310645399</v>
+        <v>1.24265127259746</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.602589868533711</v>
+        <v>4.658848245704947</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.833106360429428</v>
+        <v>-4.829102716535697</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.979196877003884</v>
+        <v>1.980798334561376</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.106042319967239</v>
+        <v>1.199806281919301</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.576421237469747</v>
+        <v>4.632679614640984</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113686</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.74489952628185</v>
+        <v>-4.740895882388119</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.034354003513234</v>
+        <v>2.035955461070726</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.106042319967239</v>
+        <v>1.199806281919301</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.596295630320066</v>
+        <v>4.652554007491303</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.79448684401644</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.638864531076541</v>
+        <v>-4.63486088718281</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.060468702120086</v>
+        <v>2.062070159677578</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.106042319967239</v>
+        <v>1.199806281919301</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.579996330844794</v>
+        <v>4.636254708016031</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.455652867943446</v>
+        <v>-4.451649224049715</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.136184316837369</v>
+        <v>2.137785774394862</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.106042319967239</v>
+        <v>1.199806281919301</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.582427280308839</v>
+        <v>4.638685657480076</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.383931420929595</v>
+        <v>-4.379927777035864</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.130664081490799</v>
+        <v>2.132265539048292</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.17776376698109</v>
+        <v>1.271527728933151</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.591251334365039</v>
+        <v>4.647509711536276</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.361558395321889</v>
+        <v>-4.357554751428157</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.086529037655053</v>
+        <v>2.088130495212546</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.189019518093991</v>
+        <v>1.282783480046053</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.544920530953952</v>
+        <v>4.601178908125189</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.71560744645673</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.394574691232633</v>
+        <v>-4.390571047338902</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.258520724176111</v>
+        <v>2.260122181733603</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.11958214142724</v>
+        <v>1.213346103379301</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.688456309839256</v>
+        <v>4.744714687010493</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.383047055583025</v>
+        <v>-4.379043411689294</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.255053004264203</v>
+        <v>2.256654461821696</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.178582799628602</v>
+        <v>1.272346761580664</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.715777930588323</v>
+        <v>4.77203630775956</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.480388556925393</v>
+        <v>-4.476384913031662</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.219784516249044</v>
+        <v>2.221385973806536</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.134162617463114</v>
+        <v>1.227926579415175</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.692793933810818</v>
+        <v>4.749052310982055</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427683</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.56624458626536</v>
+        <v>-4.562240942371629</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.186693186705896</v>
+        <v>2.188294644263388</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.091786548236979</v>
+        <v>1.18555051018904</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.668619374467975</v>
+        <v>4.724877751639212</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.575081383681479</v>
+        <v>-4.571077739787748</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.16557766955995</v>
+        <v>2.167179127117442</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.084344375595628</v>
+        <v>1.17810833754769</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.646573272703667</v>
+        <v>4.702831649874904</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.666463946246938</v>
+        <v>-4.662460302353207</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.139189155578816</v>
+        <v>2.140790613136308</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.047779490876283</v>
+        <v>1.141543452828345</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.634798852917109</v>
+        <v>4.691057230088346</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.67397837488919</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.654757228259932</v>
+        <v>-4.650753584366201</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.246000100597886</v>
+        <v>2.247601558155378</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.05948620886329</v>
+        <v>1.153250170815352</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.74395114153358</v>
+        <v>4.800209518704817</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.555093724176269</v>
+        <v>-4.551090080282538</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.288897840962755</v>
+        <v>2.290499298520248</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.122673292066976</v>
+        <v>1.216437254019038</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.784895730187197</v>
+        <v>4.841154107358435</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.189192607468328</v>
+        <v>4.180633781312596</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.565409822342621</v>
+        <v>-4.56140617844889</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.362672254217532</v>
+        <v>2.355714885619292</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.122673292066976</v>
+        <v>1.216437254019038</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.862796582708515</v>
+        <v>4.91049613372402</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762286</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.188371274380418</v>
+        <v>4.179812448224686</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.565315854325249</v>
+        <v>-4.561312210431518</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.361888508336571</v>
+        <v>2.354931139738331</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.123043153414294</v>
+        <v>1.216807115366356</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.862197166428995</v>
+        <v>4.9098967174445</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988017</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.182603260324772</v>
+        <v>4.17404443416904</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.572534678525093</v>
+        <v>-4.568531034631362</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.353232964600987</v>
+        <v>2.346275596002747</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.123043153414294</v>
+        <v>1.216807115366356</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.856429152373349</v>
+        <v>4.904128703388854</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.182603260324772</v>
+        <v>4.17404443416904</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.571586255407055</v>
+        <v>-4.567582611513323</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.353612333848202</v>
+        <v>2.346654965249963</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.123043153414294</v>
+        <v>1.216807115366356</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.856429152373349</v>
+        <v>4.904128703388854</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.195330868305864</v>
+        <v>4.186772042150132</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.728654713662678</v>
+        <v>-4.724651069768948</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.303512558527045</v>
+        <v>2.296555189928805</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.123043153414294</v>
+        <v>1.216807115366356</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.869156760354441</v>
+        <v>4.916856311369946</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.197276866730252</v>
+        <v>4.188718040574519</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.722662466873866</v>
+        <v>-4.718658822980136</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.307855455666957</v>
+        <v>2.300898087068717</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.123043153414294</v>
+        <v>1.216807115366356</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.871102758778829</v>
+        <v>4.918802309794334</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.19093100274802</v>
+        <v>4.182372176592288</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.634104505743099</v>
+        <v>-4.630100861849368</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.336932776137033</v>
+        <v>2.329975407538793</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.123043153414294</v>
+        <v>1.216807115366356</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.864756894796598</v>
+        <v>4.912456445812103</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.190239680187016</v>
+        <v>4.181680854031284</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.616345428240025</v>
+        <v>-4.612341784346294</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.343345084577258</v>
+        <v>2.336387715979019</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.123043153414294</v>
+        <v>1.216807115366356</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.864065572235593</v>
+        <v>4.911765123251098</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.203021866095603</v>
+        <v>4.194463039939871</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.516715277190957</v>
+        <v>-4.512711633297227</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.395979330905472</v>
+        <v>2.389021962307232</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.222673304463362</v>
+        <v>1.316437266415424</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.936625848773621</v>
+        <v>4.984325399789125</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.392176131594329</v>
+        <v>4.383617305438597</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.566114785879968</v>
+        <v>-4.562111141986238</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.565373792928594</v>
+        <v>2.558416424330354</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.232932137895107</v>
+        <v>1.326696099847168</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.131935414331394</v>
+        <v>5.179634965346898</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.379364804697191</v>
+        <v>4.370805978541459</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.359430312237592</v>
+        <v>-4.355426668343862</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.635236255488406</v>
+        <v>2.628278886890167</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.439616611537482</v>
+        <v>1.533380573489544</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.243134771619681</v>
+        <v>5.290834322635186</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.381366318351296</v>
+        <v>4.372807492195564</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.393587207235118</v>
+        <v>-4.389583563341388</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.623575011143501</v>
+        <v>2.616617642545261</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.35603284199667</v>
+        <v>1.449796803948732</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.194986023549299</v>
+        <v>5.242685574564804</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.734863432340964</v>
+        <v>4.726304606185232</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.300997728173662</v>
+        <v>-4.296994084279931</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.014107916757751</v>
+        <v>3.007150548159511</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.35603284199667</v>
+        <v>1.449796803948732</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.548483137538966</v>
+        <v>5.596182688554471</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.739426543908067</v>
+        <v>4.730867717752336</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.360886355997212</v>
+        <v>-4.356882712103482</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.994715577195434</v>
+        <v>2.987758208597195</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.341910927309205</v>
+        <v>1.435674889261267</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.54457310029359</v>
+        <v>5.592272651309096</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.835202441103563</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.789256485231594</v>
+        <v>4.780697659075863</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.30867004620087</v>
+        <v>-4.30466640230714</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.065432042437498</v>
+        <v>3.058474673839259</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.341910927309205</v>
+        <v>1.435674889261267</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.594403041617118</v>
+        <v>5.642102592632623</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.855626132491441</v>
+        <v>3.819982684631589</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.920534808601623</v>
+        <v>4.911975982445892</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.30867004620087</v>
+        <v>-4.20666620903882</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.065432042437498</v>
+        <v>3.228953074516616</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.341910927309205</v>
+        <v>1.533675082529587</v>
       </c>
       <c r="G2093" t="n">
-        <v>4.913598605587991</v>
+        <v>5.832181031963644</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240920.xlsx
+++ b/tame_output/ON/bt/strategyON_20240920.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>179.6%</t>
+          <t>181.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-582.2%</t>
+          <t>-591.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-55.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.5%</t>
+          <t>-319.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-70.6%</t>
+          <t>-74.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.6%</t>
+          <t>133.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>122.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>136.8%</t>
         </is>
       </c>
     </row>
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.084767712091454</v>
+        <v>-3.176955444621133</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.971312200713553</v>
+        <v>1.93443710770168</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9115533941825285</v>
+        <v>0.8727778476903187</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.752507746373399</v>
+        <v>3.729242418478074</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.112668499200927</v>
+        <v>-3.204856231730606</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.958675926996765</v>
+        <v>1.921800833984894</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8769564700395936</v>
+        <v>0.8381809235473839</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.73027363301464</v>
+        <v>3.707008305119315</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.23519460190382</v>
+        <v>-3.3273823344335</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.906429929892806</v>
+        <v>1.869554836880935</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7544303673366998</v>
+        <v>0.7156548208444901</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.653522415370103</v>
+        <v>3.630257087474777</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.465709098089409</v>
+        <v>-3.557896830619089</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.880930091009075</v>
+        <v>1.844054997997203</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.523915871151111</v>
+        <v>0.4851403246589013</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.581919677249253</v>
+        <v>3.558654349353927</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.814454183313853</v>
+        <v>-3.906641915843532</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.881743775921144</v>
+        <v>1.844868682909273</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.3763923707400035</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.656982623899762</v>
+        <v>3.633717296004436</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.968440601089993</v>
+        <v>-4.060628333619673</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.889129477956328</v>
+        <v>1.852254384944456</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.3763923707400035</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.725962893045402</v>
+        <v>3.702697565150076</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.173040035953002</v>
+        <v>-4.265227768482681</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.793340906131246</v>
+        <v>1.756465813119374</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.3763923707400035</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.712014095165522</v>
+        <v>3.688748767270197</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.425515189960726</v>
+        <v>-4.517702922490406</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.70422133358357</v>
+        <v>1.667346240571698</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.3763923707400035</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.723884584220936</v>
+        <v>3.700619256325611</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.718410946440138</v>
+        <v>-4.810598678969818</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.588273565510748</v>
+        <v>1.551398472498877</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.3763923707400035</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.72509511873988</v>
+        <v>3.701829790844554</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.905075074574946</v>
+        <v>-4.997262807104626</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.517729656484147</v>
+        <v>1.480854563472275</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3884289464076534</v>
+        <v>0.3496533999154436</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.713173478472465</v>
+        <v>3.68990815057714</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.051095761488908</v>
+        <v>-5.143283494018588</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.454399234454751</v>
+        <v>1.417524141442879</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.3405703081215867</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.702801476132341</v>
+        <v>3.679536148237015</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.142809770598493</v>
+        <v>-5.234997503128174</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.579917687509961</v>
+        <v>1.543042594498089</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.3405703081215867</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.865005532831385</v>
+        <v>3.841740204936059</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.174461429658463</v>
+        <v>-5.266649162188143</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.562103661849788</v>
+        <v>1.525228568837916</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3741773973693562</v>
+        <v>0.3354018508771465</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.856751096448535</v>
+        <v>3.833485768553209</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.243527484231399</v>
+        <v>-5.33571521676108</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.544706657589105</v>
+        <v>1.507831564577232</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3118065198757461</v>
+        <v>0.2730309733835364</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.82955798752086</v>
+        <v>3.806292659625534</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.345503606479807</v>
+        <v>-5.437691339009487</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.512841847145644</v>
+        <v>1.475966754133772</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2098303976273386</v>
+        <v>0.1710548511351289</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.777297952627718</v>
+        <v>3.754032624732392</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.235497323002585</v>
+        <v>-5.327685055532266</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.548997247780708</v>
+        <v>1.512122154768836</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2330349695446138</v>
+        <v>0.1942594230524041</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.783373583022259</v>
+        <v>3.760108255126933</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.185717071638896</v>
+        <v>-5.275662952310623</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.573159359048158</v>
+        <v>1.537181006779467</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2375293898156866</v>
+        <v>0.2009146840640496</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.790320245906877</v>
+        <v>3.768351422455894</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.884270346167058</v>
+        <v>-4.974216226838785</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.700998932119429</v>
+        <v>1.665020579850738</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5389761152875239</v>
+        <v>0.5023614095358868</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.978449164072515</v>
+        <v>3.956480340621533</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.908860590402242</v>
+        <v>-4.998806471073969</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.692134012178066</v>
+        <v>1.656155659909375</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5389761152875239</v>
+        <v>0.5023614095358868</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.979420341825225</v>
+        <v>3.957451518374243</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.857822214395722</v>
+        <v>-4.947768095067449</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.71339226696043</v>
+        <v>1.677413914691739</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5389761152875239</v>
+        <v>0.5023614095358868</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.980263246204981</v>
+        <v>3.958294422753998</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.816682919529091</v>
+        <v>-4.906628800200818</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.748886083781227</v>
+        <v>1.712907731512537</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5801154101541547</v>
+        <v>0.5435007044025176</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.023984921999105</v>
+        <v>4.002016098548123</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.720048007510451</v>
+        <v>-4.809993888182178</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.603724044712618</v>
+        <v>1.567745692443927</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6767503221727946</v>
+        <v>0.6401356164211576</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.898149865334223</v>
+        <v>3.876181041883241</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.651009996561983</v>
+        <v>-4.74095587723371</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.634841293165969</v>
+        <v>1.598862940897279</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7457883331212627</v>
+        <v>0.7091736273696256</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.943074715977269</v>
+        <v>3.921105892526286</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.486513662371022</v>
+        <v>-4.576459543042748</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.685066645918436</v>
+        <v>1.649088293649746</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9102846673122246</v>
+        <v>0.8736699615605875</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.026199335567928</v>
+        <v>4.004230512116946</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.409415060829149</v>
+        <v>-4.499360941500876</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.715093796971615</v>
+        <v>1.679115444702925</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9102846673122246</v>
+        <v>0.8736699615605875</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.025387046004358</v>
+        <v>4.003418222553376</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.419800255719038</v>
+        <v>-4.509746136390765</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.720808498140732</v>
+        <v>1.684830145872041</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8998994724223353</v>
+        <v>0.8632847666706982</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.029024708195497</v>
+        <v>4.007055884744514</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.438388414441263</v>
+        <v>-4.52833429511299</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.784210240428267</v>
+        <v>1.748231888159576</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8813113137001098</v>
+        <v>0.8446966079484728</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.088708818738587</v>
+        <v>4.066739995287604</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.438686961137299</v>
+        <v>-4.528632841809026</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.780959832568151</v>
+        <v>1.744981480299461</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8810127670040739</v>
+        <v>0.8443980612524369</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.085398701539264</v>
+        <v>4.063429878088281</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.337863827446871</v>
+        <v>-4.427809708118598</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.825819980983714</v>
+        <v>1.789841628715023</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8934769824884278</v>
+        <v>0.8568622767367907</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.097408125769267</v>
+        <v>4.075439302318285</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.147082466694464</v>
+        <v>-4.237028347366191</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.90226177876322</v>
+        <v>1.866283426494529</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.084258343240835</v>
+        <v>1.047643637489198</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.212006195699255</v>
+        <v>4.190037372248272</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.040119108845042</v>
+        <v>-4.13006498951677</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.924883967640585</v>
+        <v>1.888905615371894</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.142722951200636</v>
+        <v>1.106108245449</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.226921806212732</v>
+        <v>4.20495298276175</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.98478852094328</v>
+        <v>-4.074734401615007</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.981983139413348</v>
+        <v>1.946004787144658</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.198053539102399</v>
+        <v>1.161438833350762</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.295087095565848</v>
+        <v>4.273118272114866</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.972734394030317</v>
+        <v>-4.062680274702045</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.980491358079972</v>
+        <v>1.944513005811281</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.210107666015361</v>
+        <v>1.173492960263725</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.296006139615064</v>
+        <v>4.274037316164081</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.013889513598539</v>
+        <v>-4.103835394270265</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.965909940436819</v>
+        <v>1.929931588168128</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.16895254644714</v>
+        <v>1.132337840695504</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.273193698058266</v>
+        <v>4.251224874607285</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.945840950907009</v>
+        <v>-4.035786831578736</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.005980391391313</v>
+        <v>1.970002039122623</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.23700110913867</v>
+        <v>1.200386403387034</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.326873861551067</v>
+        <v>4.304905038100085</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.177441344076509</v>
+        <v>-4.267387224748236</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.933542904297107</v>
+        <v>1.897564552028416</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.23700110913867</v>
+        <v>1.200386403387034</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.347076531724661</v>
+        <v>4.325107708273679</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.227492889605729</v>
+        <v>-4.317438770277455</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.897128522152301</v>
+        <v>1.861150169883611</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.23700110913867</v>
+        <v>1.200386403387034</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.330682767791544</v>
+        <v>4.308713944340561</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.402599722182174</v>
+        <v>-4.4925456028539</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.78733770271519</v>
+        <v>1.751359350446499</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.23700110913867</v>
+        <v>1.200386403387034</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.29093468138501</v>
+        <v>4.268965857934027</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.206499568751651</v>
+        <v>-4.296445449423377</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.872800383084339</v>
+        <v>1.836822030815649</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.433101262569193</v>
+        <v>1.396486556817556</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.415617392440264</v>
+        <v>4.393648568989281</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.053474176638367</v>
+        <v>-4.143420057310093</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.033181539502557</v>
+        <v>1.997203187233867</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.586126654682477</v>
+        <v>1.54951194893084</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.606603627281139</v>
+        <v>4.584634803830157</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.081781490511637</v>
+        <v>-4.171727371183363</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.209324838861542</v>
+        <v>2.173346486592851</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.586126654682477</v>
+        <v>1.54951194893084</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.794069852189431</v>
+        <v>4.772101028738449</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.248374715625159</v>
+        <v>-4.338320596296885</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.112090500170216</v>
+        <v>2.076112147901525</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.419533429568955</v>
+        <v>1.382918723817318</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.6635168684754</v>
+        <v>4.641548045024418</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.225338922263593</v>
+        <v>-4.315284802935319</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.12498122017656</v>
+        <v>2.089002867907869</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.419533429568955</v>
+        <v>1.382918723817318</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.667193271137118</v>
+        <v>4.645224447686136</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.196092941807897</v>
+        <v>-4.286038822479623</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.134297667482334</v>
+        <v>2.098319315213643</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.419533429568955</v>
+        <v>1.382918723817318</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.664811326260613</v>
+        <v>4.642842502809631</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.303018489685748</v>
+        <v>-4.392964370357474</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.088820687488828</v>
+        <v>2.052842335220138</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.312607881691104</v>
+        <v>1.275993175939467</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.597949236691537</v>
+        <v>4.575980413240556</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.448037048192997</v>
+        <v>-4.537982928864722</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.032242066229163</v>
+        <v>1.996263713960472</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.167589323183855</v>
+        <v>1.130974617432218</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.512366903730423</v>
+        <v>4.490398080279441</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.566378813977714</v>
+        <v>-4.65632469464944</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.084836599173029</v>
+        <v>2.048858246904338</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.178275361746745</v>
+        <v>1.141660655995108</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.61870976612591</v>
+        <v>4.596740942674928</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.617789236298422</v>
+        <v>-4.707735116970148</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.062058127370685</v>
+        <v>2.026079775101994</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.178275361746745</v>
+        <v>1.141660655995108</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.616495463251849</v>
+        <v>4.594526639800867</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.697208687506174</v>
+        <v>-4.7871545681779</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.030193474961873</v>
+        <v>1.994215122693183</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.178275361746745</v>
+        <v>1.141660655995108</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.616398591326139</v>
+        <v>4.594429767875156</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.792671685423391</v>
+        <v>-4.882617566095117</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.992002169353029</v>
+        <v>1.956023817084339</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.178275361746745</v>
+        <v>1.141660655995108</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.616392484884181</v>
+        <v>4.594423661433199</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217999</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.728295774572676</v>
+        <v>-4.818241655244402</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.015848930255926</v>
+        <v>1.979870577987235</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.24265127259746</v>
+        <v>1.206036566845823</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.65311442795722</v>
+        <v>4.631145604506239</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353534</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.78366493670487</v>
+        <v>-4.873610817376596</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.999435083150775</v>
+        <v>1.963456730882084</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.24265127259746</v>
+        <v>1.206036566845823</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.658848245704947</v>
+        <v>4.636879422253966</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.829102716535697</v>
+        <v>-4.919048597207423</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.980798334561376</v>
+        <v>1.944819982292686</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.199806281919301</v>
+        <v>1.163191576167664</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.632679614640984</v>
+        <v>4.610710791190002</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113686</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.740895882388119</v>
+        <v>-4.830841763059845</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.035955461070726</v>
+        <v>1.999977108802036</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.199806281919301</v>
+        <v>1.163191576167664</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.652554007491303</v>
+        <v>4.630585184040321</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79448684401644</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.63486088718281</v>
+        <v>-4.724806767854536</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.062070159677578</v>
+        <v>2.026091807408887</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.199806281919301</v>
+        <v>1.163191576167664</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.636254708016031</v>
+        <v>4.614285884565049</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.451649224049715</v>
+        <v>-4.54159510472144</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.137785774394862</v>
+        <v>2.101807422126171</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.199806281919301</v>
+        <v>1.163191576167664</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.638685657480076</v>
+        <v>4.616716834029094</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.379927777035864</v>
+        <v>-4.469873657707589</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.132265539048292</v>
+        <v>2.096287186779601</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.271527728933151</v>
+        <v>1.234913023181515</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.647509711536276</v>
+        <v>4.625540888085294</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.357554751428157</v>
+        <v>-4.447500632099883</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.088130495212546</v>
+        <v>2.052152142943855</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.282783480046053</v>
+        <v>1.246168774294416</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.601178908125189</v>
+        <v>4.579210084674207</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71560744645673</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.390571047338902</v>
+        <v>-4.480516928010628</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.260122181733603</v>
+        <v>2.224143829464913</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.213346103379301</v>
+        <v>1.176731397627665</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.744714687010493</v>
+        <v>4.722745863559511</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.379043411689294</v>
+        <v>-4.468989292361019</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.256654461821696</v>
+        <v>2.220676109553005</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.272346761580664</v>
+        <v>1.235732055829027</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.77203630775956</v>
+        <v>4.750067484308578</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.476384913031662</v>
+        <v>-4.566330793703388</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.221385973806536</v>
+        <v>2.185407621537847</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.227926579415175</v>
+        <v>1.191311873663539</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.749052310982055</v>
+        <v>4.727083487531073</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427683</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.562240942371629</v>
+        <v>-4.652186823043355</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.188294644263388</v>
+        <v>2.152316291994698</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.18555051018904</v>
+        <v>1.148935804437404</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.724877751639212</v>
+        <v>4.70290892818823</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610382</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.571077739787748</v>
+        <v>-4.661023620459474</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.167179127117442</v>
+        <v>2.131200774848752</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.17810833754769</v>
+        <v>1.141493631796053</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.702831649874904</v>
+        <v>4.680862826423922</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.662460302353207</v>
+        <v>-4.752406183024933</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.140790613136308</v>
+        <v>2.104812260867618</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.141543452828345</v>
+        <v>1.104928747076708</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.691057230088346</v>
+        <v>4.669088406637364</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.67397837488919</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.650753584366201</v>
+        <v>-4.740699465037927</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.247601558155378</v>
+        <v>2.211623205886688</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.153250170815352</v>
+        <v>1.116635465063715</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.800209518704817</v>
+        <v>4.778240695253835</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.551090080282538</v>
+        <v>-4.641035960954264</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.290499298520248</v>
+        <v>2.254520946251557</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.216437254019038</v>
+        <v>1.179822548267401</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.841154107358435</v>
+        <v>4.819185283907452</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.180633781312596</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.56140617844889</v>
+        <v>-4.651352059120616</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.355714885619292</v>
+        <v>2.463299340263075</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.216437254019038</v>
+        <v>1.179822548267401</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.91049613372402</v>
+        <v>5.03209011718551</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762286</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.179812448224686</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.561312210431518</v>
+        <v>-4.651258091103244</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.354931139738331</v>
+        <v>2.462515594382114</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.216807115366356</v>
+        <v>1.180192409614719</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.9098967174445</v>
+        <v>5.031490700905991</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988017</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.17404443416904</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.568531034631362</v>
+        <v>-4.658476915303088</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.346275596002747</v>
+        <v>2.453860050646529</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.216807115366356</v>
+        <v>1.180192409614719</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.904128703388854</v>
+        <v>5.025722686850345</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.17404443416904</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.567582611513323</v>
+        <v>-4.657528492185049</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.346654965249963</v>
+        <v>2.454239419893745</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.216807115366356</v>
+        <v>1.180192409614719</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.904128703388854</v>
+        <v>5.025722686850345</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.186772042150132</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.724651069768948</v>
+        <v>-4.814596950440674</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.296555189928805</v>
+        <v>2.404139644572587</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.216807115366356</v>
+        <v>1.180192409614719</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.916856311369946</v>
+        <v>5.038450294831437</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.188718040574519</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.718658822980136</v>
+        <v>-4.808604703651862</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.300898087068717</v>
+        <v>2.4084825417125</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.216807115366356</v>
+        <v>1.180192409614719</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.918802309794334</v>
+        <v>5.040396293255824</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.182372176592288</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.630100861849368</v>
+        <v>-4.720046742521094</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.329975407538793</v>
+        <v>2.437559862182575</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.216807115366356</v>
+        <v>1.180192409614719</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.912456445812103</v>
+        <v>5.034050429273593</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.181680854031284</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.612341784346294</v>
+        <v>-4.70228766501802</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.336387715979019</v>
+        <v>2.443972170622801</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.216807115366356</v>
+        <v>1.180192409614719</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.911765123251098</v>
+        <v>5.033359106712589</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.194463039939871</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.512711633297227</v>
+        <v>-4.602657513968953</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.389021962307232</v>
+        <v>2.496606416951015</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.316437266415424</v>
+        <v>1.279822560663787</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.984325399789125</v>
+        <v>5.105919383250616</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.383617305438597</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.562111141986238</v>
+        <v>-4.652057022657964</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.558416424330354</v>
+        <v>2.666000878974137</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.326696099847168</v>
+        <v>1.290081394095532</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.179634965346898</v>
+        <v>5.301228948808389</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.370805978541459</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.355426668343862</v>
+        <v>-4.445372549015588</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.628278886890167</v>
+        <v>2.735863341533949</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.533380573489544</v>
+        <v>1.496765867737907</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.290834322635186</v>
+        <v>5.412428306096677</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.372807492195564</v>
+        <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.389583563341388</v>
+        <v>-4.479529444013114</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.616617642545261</v>
+        <v>2.724202097189043</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.449796803948732</v>
+        <v>1.413182098197095</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.242685574564804</v>
+        <v>5.364279558026294</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.726304606185232</v>
+        <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.296994084279931</v>
+        <v>-4.386939964951657</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.007150548159511</v>
+        <v>3.114735002803294</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.449796803948732</v>
+        <v>1.413182098197095</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.596182688554471</v>
+        <v>5.717776672015962</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.730867717752336</v>
+        <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.356882712103482</v>
+        <v>-4.446828592775208</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.987758208597195</v>
+        <v>3.095342663240977</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.435674889261267</v>
+        <v>1.39906018350963</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.592272651309096</v>
+        <v>5.713866634770586</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103563</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.780697659075863</v>
+        <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.30466640230714</v>
+        <v>-4.394612282978866</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.058474673839259</v>
+        <v>3.166059128483041</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.435674889261267</v>
+        <v>1.39906018350963</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.642102592632623</v>
+        <v>5.763696576094114</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.819982684631589</v>
+        <v>3.715499073708515</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.911975982445892</v>
+        <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.20666620903882</v>
+        <v>-4.30131607425692</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.228953074516616</v>
+        <v>3.212191582181831</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.533675082529587</v>
+        <v>1.492356392231576</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.832181031963644</v>
+        <v>5.828488271537292</v>
       </c>
     </row>
   </sheetData>
